--- a/docs/compound_genes_clusters.xlsx
+++ b/docs/compound_genes_clusters.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -421,6 +421,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>comparison_description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,19 +450,19 @@
         <v>619.6378019790453</v>
       </c>
       <c r="F2">
-        <v>-2.832667636181228</v>
+        <v>-2.832667636146422</v>
       </c>
       <c r="G2">
-        <v>0.5545186749772185</v>
+        <v>0.5545186730020781</v>
       </c>
       <c r="H2">
-        <v>-5.108335866772393</v>
+        <v>-5.108335884905008</v>
       </c>
       <c r="I2">
-        <v>3.250085529796281E-07</v>
+        <v>3.250085217962947E-07</v>
       </c>
       <c r="J2">
-        <v>1.13119008248941E-05</v>
+        <v>1.131189973956028E-05</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -472,6 +477,11 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Fc fragment of IgE receptor Ig [Source:HGNC Symbol;Acc:HGNC:3611]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -498,19 +508,19 @@
         <v>418.9459802987127</v>
       </c>
       <c r="F3">
-        <v>-2.665627564310894</v>
+        <v>-2.665627564244736</v>
       </c>
       <c r="G3">
-        <v>0.5769333480472648</v>
+        <v>0.576933345738678</v>
       </c>
       <c r="H3">
-        <v>-4.620338854277001</v>
+        <v>-4.620338872650518</v>
       </c>
       <c r="I3">
-        <v>3.831138115645387E-06</v>
+        <v>3.831137776352424E-06</v>
       </c>
       <c r="J3">
-        <v>9.263357783358777E-05</v>
+        <v>9.263356962977989E-05</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -525,6 +535,11 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>allograft inflammatory factor 1 [Source:HGNC Symbol;Acc:HGNC:352]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -551,19 +566,19 @@
         <v>281.8852773909378</v>
       </c>
       <c r="F4">
-        <v>-1.859385972272716</v>
+        <v>-1.85938597229601</v>
       </c>
       <c r="G4">
-        <v>0.4768229983884031</v>
+        <v>0.4768229997881319</v>
       </c>
       <c r="H4">
-        <v>-3.899530808197564</v>
+        <v>-3.899530796799223</v>
       </c>
       <c r="I4">
-        <v>9.637927372540167E-05</v>
+        <v>9.637927826238126E-05</v>
       </c>
       <c r="J4">
-        <v>0.001393012538211741</v>
+        <v>0.001393012603786726</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -578,6 +593,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>G protein-coupled receptor kinase 5 [Source:HGNC Symbol;Acc:HGNC:4544]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -604,19 +624,19 @@
         <v>661.9901485341281</v>
       </c>
       <c r="F5">
-        <v>-2.442983995884801</v>
+        <v>-2.442983995891172</v>
       </c>
       <c r="G5">
-        <v>0.4704580513981956</v>
+        <v>0.4704580520378944</v>
       </c>
       <c r="H5">
-        <v>-5.192777525274107</v>
+        <v>-5.192777518226842</v>
       </c>
       <c r="I5">
-        <v>2.071797032509361E-07</v>
+        <v>2.071797110960398E-07</v>
       </c>
       <c r="J5">
-        <v>7.796825386076204E-06</v>
+        <v>7.796823617827616E-06</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -631,6 +651,11 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Spi-1 proto-oncogene [Source:HGNC Symbol;Acc:HGNC:11241]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -657,19 +682,19 @@
         <v>592.9448009967771</v>
       </c>
       <c r="F6">
-        <v>-2.66155400362357</v>
+        <v>-2.661554003586477</v>
       </c>
       <c r="G6">
-        <v>0.5475600762600275</v>
+        <v>0.5475600747344824</v>
       </c>
       <c r="H6">
-        <v>-4.860752489119826</v>
+        <v>-4.860752502594518</v>
       </c>
       <c r="I6">
-        <v>1.169403886086399E-06</v>
+        <v>1.169403806481549E-06</v>
       </c>
       <c r="J6">
-        <v>3.312528562722477E-05</v>
+        <v>3.312528337228665E-05</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -684,6 +709,11 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>adhesion G protein-coupled receptor E5 [Source:HGNC Symbol;Acc:HGNC:1711]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -710,19 +740,19 @@
         <v>599.7709540929075</v>
       </c>
       <c r="F7">
-        <v>-1.912472523092463</v>
+        <v>-1.912472523089822</v>
       </c>
       <c r="G7">
-        <v>0.4958533825523085</v>
+        <v>0.4958533824012598</v>
       </c>
       <c r="H7">
-        <v>-3.85693148496514</v>
+        <v>-3.856931486134727</v>
       </c>
       <c r="I7">
-        <v>0.0001148193288364019</v>
+        <v>0.0001148193282872307</v>
       </c>
       <c r="J7">
-        <v>0.001627862926844188</v>
+        <v>0.00162786303617929</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -737,6 +767,11 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>integrin subunit beta 2 [Source:HGNC Symbol;Acc:HGNC:6155]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -763,19 +798,19 @@
         <v>3357.83495428662</v>
       </c>
       <c r="F8">
-        <v>-3.194865198506743</v>
+        <v>-3.19486519848973</v>
       </c>
       <c r="G8">
-        <v>0.5450676362396815</v>
+        <v>0.5450676340999403</v>
       </c>
       <c r="H8">
-        <v>-5.861410559150995</v>
+        <v>-5.86141058212959</v>
       </c>
       <c r="I8">
-        <v>4.589516622129246E-09</v>
+        <v>4.589515986909703E-09</v>
       </c>
       <c r="J8">
-        <v>3.031619852140948E-07</v>
+        <v>3.031619432544652E-07</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -790,6 +825,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>complement C1q A chain [Source:HGNC Symbol;Acc:HGNC:1241]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -816,19 +856,19 @@
         <v>289.1993123722151</v>
       </c>
       <c r="F9">
-        <v>-4.00477230230169</v>
+        <v>-4.004772302163957</v>
       </c>
       <c r="G9">
-        <v>0.5497597051671511</v>
+        <v>0.5497597042034894</v>
       </c>
       <c r="H9">
-        <v>-7.284586819770764</v>
+        <v>-7.284586832289222</v>
       </c>
       <c r="I9">
-        <v>3.226576350711432E-13</v>
+        <v>3.226576051120957E-13</v>
       </c>
       <c r="J9">
-        <v>5.565127188010396E-11</v>
+        <v>5.565126671283402E-11</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -843,6 +883,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>olfactomedin like 3 [Source:HGNC Symbol;Acc:HGNC:24956]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -869,19 +914,19 @@
         <v>182.9276932123608</v>
       </c>
       <c r="F10">
-        <v>-2.819454650013005</v>
+        <v>-2.819454649992519</v>
       </c>
       <c r="G10">
-        <v>0.5567465145678088</v>
+        <v>0.5567465140707757</v>
       </c>
       <c r="H10">
-        <v>-5.064162192738093</v>
+        <v>-5.064162197222306</v>
       </c>
       <c r="I10">
-        <v>4.102003061402073E-07</v>
+        <v>4.102002964858163E-07</v>
       </c>
       <c r="J10">
-        <v>1.369363301551492E-05</v>
+        <v>1.369363269322436E-05</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -896,6 +941,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>HCK proto-oncogene, Src family tyrosine kinase [Source:HGNC Symbol;Acc:HGNC:4840]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -922,19 +972,19 @@
         <v>831.9388251401573</v>
       </c>
       <c r="F11">
-        <v>-3.118726805920342</v>
+        <v>-3.118726805907785</v>
       </c>
       <c r="G11">
-        <v>0.5052794159837362</v>
+        <v>0.5052794153763416</v>
       </c>
       <c r="H11">
-        <v>-6.172281528327145</v>
+        <v>-6.17228153572197</v>
       </c>
       <c r="I11">
-        <v>6.731150424114175E-10</v>
+        <v>6.731150109196776E-10</v>
       </c>
       <c r="J11">
-        <v>5.741079562281557E-08</v>
+        <v>5.7410792936847E-08</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -949,6 +999,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>membrane spanning 4-domains A6A [Source:HGNC Symbol;Acc:HGNC:13375]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -975,19 +1030,19 @@
         <v>585.3858598197312</v>
       </c>
       <c r="F12">
-        <v>-3.237894881431413</v>
+        <v>-3.237894881241027</v>
       </c>
       <c r="G12">
-        <v>0.6038933904687034</v>
+        <v>0.6038933872137069</v>
       </c>
       <c r="H12">
-        <v>-5.361699486259266</v>
+        <v>-5.361699514843661</v>
       </c>
       <c r="I12">
-        <v>8.244261078082707E-08</v>
+        <v>8.244259773237702E-08</v>
       </c>
       <c r="J12">
-        <v>3.564781746938102E-06</v>
+        <v>3.564781182728937E-06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1002,6 +1057,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>phospholipid transfer protein [Source:HGNC Symbol;Acc:HGNC:9093]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1028,19 +1088,19 @@
         <v>83.42781461788584</v>
       </c>
       <c r="F13">
-        <v>-2.456363989384324</v>
+        <v>-2.45636398924531</v>
       </c>
       <c r="G13">
-        <v>0.6445433231987019</v>
+        <v>0.6445433223086349</v>
       </c>
       <c r="H13">
-        <v>-3.811014560191275</v>
+        <v>-3.811014565238329</v>
       </c>
       <c r="I13">
-        <v>0.0001383976143777929</v>
+        <v>0.0001383976115518205</v>
       </c>
       <c r="J13">
-        <v>0.00190625214550708</v>
+        <v>0.001906252106582883</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1055,6 +1115,11 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>runt related transcription factor 3 [Source:HGNC Symbol;Acc:HGNC:10473]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1081,19 +1146,19 @@
         <v>1099.100035924536</v>
       </c>
       <c r="F14">
-        <v>-3.432562077771046</v>
+        <v>-3.432562077798971</v>
       </c>
       <c r="G14">
-        <v>0.4497825317390397</v>
+        <v>0.4497825328433207</v>
       </c>
       <c r="H14">
-        <v>-7.631603798616599</v>
+        <v>-7.631603779941996</v>
       </c>
       <c r="I14">
-        <v>2.318510533234987E-14</v>
+        <v>2.318510869156061E-14</v>
       </c>
       <c r="J14">
-        <v>4.998644306584264E-12</v>
+        <v>4.998645030820769E-12</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1108,6 +1173,11 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>elastin microfibril interfacer 1 [Source:HGNC Symbol;Acc:HGNC:19880]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1134,19 +1204,19 @@
         <v>229.0062262164109</v>
       </c>
       <c r="F15">
-        <v>-3.366938948647057</v>
+        <v>-3.366938948478697</v>
       </c>
       <c r="G15">
-        <v>0.6139490832252009</v>
+        <v>0.6139490805100219</v>
       </c>
       <c r="H15">
-        <v>-5.484068696641476</v>
+        <v>-5.484068720620449</v>
       </c>
       <c r="I15">
-        <v>4.156532397690547E-08</v>
+        <v>4.156531833968146E-08</v>
       </c>
       <c r="J15">
-        <v>1.998239777526248E-06</v>
+        <v>1.99823950131197E-06</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1161,6 +1231,11 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>MAGI2 antisense RNA 3 [Source:HGNC Symbol;Acc:HGNC:40862]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1187,19 +1262,19 @@
         <v>684.8921544339628</v>
       </c>
       <c r="F16">
-        <v>-5.333158820417573</v>
+        <v>-5.333158817749234</v>
       </c>
       <c r="G16">
-        <v>0.7762865114045613</v>
+        <v>0.7762865025575886</v>
       </c>
       <c r="H16">
-        <v>-6.870090800325912</v>
+        <v>-6.870090875183799</v>
       </c>
       <c r="I16">
-        <v>6.416105204908177E-12</v>
+        <v>6.416101838010031E-12</v>
       </c>
       <c r="J16">
-        <v>8.512581290238431E-10</v>
+        <v>8.512576823199121E-10</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1214,6 +1289,11 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>proline and arginine rich end leucine rich repeat protein [Source:HGNC Symbol;Acc:HGNC:9357]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1240,19 +1320,19 @@
         <v>942.2048779003377</v>
       </c>
       <c r="F17">
-        <v>-1.936003293947557</v>
+        <v>-1.936003293951474</v>
       </c>
       <c r="G17">
-        <v>0.4708469276670341</v>
+        <v>0.4708469280787251</v>
       </c>
       <c r="H17">
-        <v>-4.111746684936698</v>
+        <v>-4.11174668134986</v>
       </c>
       <c r="I17">
-        <v>3.926770079983232E-05</v>
+        <v>3.926770141001581E-05</v>
       </c>
       <c r="J17">
-        <v>0.0006484601271444649</v>
+        <v>0.0006484601372209312</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1267,6 +1347,11 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>fatty acid hydroxylase domain containing 2 [Source:HGNC Symbol;Acc:HGNC:1334]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1293,19 +1378,19 @@
         <v>55.77555251418995</v>
       </c>
       <c r="F18">
-        <v>-2.915986667593353</v>
+        <v>-2.91598666593285</v>
       </c>
       <c r="G18">
-        <v>0.8296897267736758</v>
+        <v>0.8296897214678119</v>
       </c>
       <c r="H18">
-        <v>-3.514550769397173</v>
+        <v>-3.514550789871364</v>
       </c>
       <c r="I18">
-        <v>0.0004404984618518099</v>
+        <v>0.0004404984278947963</v>
       </c>
       <c r="J18">
-        <v>0.004842675370627227</v>
+        <v>0.004842674997316518</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1320,6 +1405,11 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>sialophorin [Source:HGNC Symbol;Acc:HGNC:11249]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1346,19 +1436,19 @@
         <v>11716.51830555458</v>
       </c>
       <c r="F19">
-        <v>-2.002188926059604</v>
+        <v>-2.002188926059747</v>
       </c>
       <c r="G19">
-        <v>0.4653642380484169</v>
+        <v>0.4653642382003061</v>
       </c>
       <c r="H19">
-        <v>-4.302412524125445</v>
+        <v>-4.302412522721498</v>
       </c>
       <c r="I19">
-        <v>1.689483803801511E-05</v>
+        <v>1.689483814510089E-05</v>
       </c>
       <c r="J19">
-        <v>0.0003213953074315056</v>
+        <v>0.0003213953094686288</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1373,6 +1463,11 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>thymosin beta 4 X-linked [Source:HGNC Symbol;Acc:HGNC:11881]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1399,19 +1494,19 @@
         <v>1737.146589276621</v>
       </c>
       <c r="F20">
-        <v>-1.55258121542105</v>
+        <v>-1.55258121542187</v>
       </c>
       <c r="G20">
-        <v>0.3740478379502291</v>
+        <v>0.3740478418305161</v>
       </c>
       <c r="H20">
-        <v>-4.150755753406165</v>
+        <v>-4.150755710349362</v>
       </c>
       <c r="I20">
-        <v>3.313792484872143E-05</v>
+        <v>3.313793108321658E-05</v>
       </c>
       <c r="J20">
-        <v>0.0005628008833990183</v>
+        <v>0.0005628009892831193</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1426,6 +1521,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>latent transforming growth factor beta binding protein 4 [Source:HGNC Symbol;Acc:HGNC:6717]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1452,19 +1552,19 @@
         <v>1942.865156359946</v>
       </c>
       <c r="F21">
-        <v>-1.117328089200595</v>
+        <v>-1.11732808919947</v>
       </c>
       <c r="G21">
-        <v>0.3367243457901943</v>
+        <v>0.3367243515213031</v>
       </c>
       <c r="H21">
-        <v>-3.318227812065536</v>
+        <v>-3.318227755585362</v>
       </c>
       <c r="I21">
-        <v>0.0009059056619732347</v>
+        <v>0.0009059058451654196</v>
       </c>
       <c r="J21">
-        <v>0.008701963855699581</v>
+        <v>0.008701965615410152</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1479,6 +1579,11 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>ring finger protein 130 [Source:HGNC Symbol;Acc:HGNC:18280]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1505,19 +1610,19 @@
         <v>1925.111194229988</v>
       </c>
       <c r="F22">
-        <v>-3.917032120293007</v>
+        <v>-3.917032120259946</v>
       </c>
       <c r="G22">
-        <v>0.5493096780664719</v>
+        <v>0.5493096760868997</v>
       </c>
       <c r="H22">
-        <v>-7.130826702490772</v>
+        <v>-7.130826728128269</v>
       </c>
       <c r="I22">
-        <v>9.976786799596224E-13</v>
+        <v>9.976784941094302E-13</v>
       </c>
       <c r="J22">
-        <v>1.56434001505184E-10</v>
+        <v>1.564339723642493E-10</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1532,6 +1637,11 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>H19, imprinted maternally expressed transcript [Source:HGNC Symbol;Acc:HGNC:4713]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1558,19 +1668,19 @@
         <v>106.7656983084645</v>
       </c>
       <c r="F23">
-        <v>-2.034942192905925</v>
+        <v>-2.034942192781968</v>
       </c>
       <c r="G23">
-        <v>0.6178754237572197</v>
+        <v>0.6178754227487692</v>
       </c>
       <c r="H23">
-        <v>-3.293450612635969</v>
+        <v>-3.293450617810679</v>
       </c>
       <c r="I23">
-        <v>0.0009896572621687532</v>
+        <v>0.0009896572439520551</v>
       </c>
       <c r="J23">
-        <v>0.009310575564027609</v>
+        <v>0.009310575392647123</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1585,6 +1695,11 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>cystatin F [Source:HGNC Symbol;Acc:HGNC:2479]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1611,19 +1726,19 @@
         <v>321.6771202959935</v>
       </c>
       <c r="F24">
-        <v>-1.843179954555603</v>
+        <v>-1.843179954513084</v>
       </c>
       <c r="G24">
-        <v>0.5519657886764162</v>
+        <v>0.5519657873716334</v>
       </c>
       <c r="H24">
-        <v>-3.339301080553286</v>
+        <v>-3.339301088369973</v>
       </c>
       <c r="I24">
-        <v>0.0008398947927505086</v>
+        <v>0.000839894769114795</v>
       </c>
       <c r="J24">
-        <v>0.008225669948180534</v>
+        <v>0.008225669716699661</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1638,6 +1753,11 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>lymphocyte specific protein 1 [Source:HGNC Symbol;Acc:HGNC:6707]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1664,19 +1784,19 @@
         <v>41.656187135119</v>
       </c>
       <c r="F25">
-        <v>-3.278734248012188</v>
+        <v>-3.278734248047756</v>
       </c>
       <c r="G25">
-        <v>0.7673647035118153</v>
+        <v>0.7673647035826178</v>
       </c>
       <c r="H25">
-        <v>-4.272719650782979</v>
+        <v>-4.272719650435099</v>
       </c>
       <c r="I25">
-        <v>1.931031796036923E-05</v>
+        <v>1.931031799050625E-05</v>
       </c>
       <c r="J25">
-        <v>0.0003568500782128708</v>
+        <v>0.0003568500787697959</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1691,6 +1811,11 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>semaphorin 6D [Source:HGNC Symbol;Acc:HGNC:16770]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1717,19 +1842,19 @@
         <v>274.3535700987542</v>
       </c>
       <c r="F26">
-        <v>-1.539043650095068</v>
+        <v>-1.53904365018773</v>
       </c>
       <c r="G26">
-        <v>0.4665901859873992</v>
+        <v>0.4665901877884807</v>
       </c>
       <c r="H26">
-        <v>-3.298491259172415</v>
+        <v>-3.298491246638526</v>
       </c>
       <c r="I26">
-        <v>0.0009720590640328214</v>
+        <v>0.0009720591074292759</v>
       </c>
       <c r="J26">
-        <v>0.009206389780952706</v>
+        <v>0.009206390191961348</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1744,6 +1869,11 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>transmembrane channel like 8 [Source:HGNC Symbol;Acc:HGNC:20474]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1770,19 +1900,19 @@
         <v>134.6913910440996</v>
       </c>
       <c r="F27">
-        <v>-2.204145004688022</v>
+        <v>-2.204145004697635</v>
       </c>
       <c r="G27">
-        <v>0.561348206621526</v>
+        <v>0.5613482067260201</v>
       </c>
       <c r="H27">
-        <v>-3.926520079138879</v>
+        <v>-3.926520078425088</v>
       </c>
       <c r="I27">
-        <v>8.618370079275737E-05</v>
+        <v>8.618370104839833E-05</v>
       </c>
       <c r="J27">
-        <v>0.001264938408539376</v>
+        <v>0.001264938614127167</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1797,6 +1927,11 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>tetraspanin 12 [Source:HGNC Symbol;Acc:HGNC:21641]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1823,19 +1958,19 @@
         <v>511.4568255622406</v>
       </c>
       <c r="F28">
-        <v>-2.024783318306842</v>
+        <v>-2.024783318353134</v>
       </c>
       <c r="G28">
-        <v>0.4065006120599002</v>
+        <v>0.4065006153713681</v>
       </c>
       <c r="H28">
-        <v>-4.981009273384511</v>
+        <v>-4.981009232921694</v>
       </c>
       <c r="I28">
-        <v>6.325350834261881E-07</v>
+        <v>6.3253521570026E-07</v>
       </c>
       <c r="J28">
-        <v>1.971655040165606E-05</v>
+        <v>1.971655452472919E-05</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1850,6 +1985,11 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>fascin actin-bundling protein 1 [Source:HGNC Symbol;Acc:HGNC:11148]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1876,19 +2016,19 @@
         <v>167.377164398068</v>
       </c>
       <c r="F29">
-        <v>-1.913539726869151</v>
+        <v>-1.913539726961639</v>
       </c>
       <c r="G29">
-        <v>0.500919575149987</v>
+        <v>0.5009195767828737</v>
       </c>
       <c r="H29">
-        <v>-3.820053800644928</v>
+        <v>-3.820053788377037</v>
       </c>
       <c r="I29">
-        <v>0.0001334225679928766</v>
+        <v>0.0001334225746291051</v>
       </c>
       <c r="J29">
-        <v>0.001847027158220272</v>
+        <v>0.001847027110554449</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1903,6 +2043,11 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>GTPase, IMAP family member 8 [Source:HGNC Symbol;Acc:HGNC:21792]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1929,19 +2074,19 @@
         <v>439.8584961393698</v>
       </c>
       <c r="F30">
-        <v>-2.541764814971391</v>
+        <v>-2.541764814682538</v>
       </c>
       <c r="G30">
-        <v>0.7610922902071985</v>
+        <v>0.7610922826273236</v>
       </c>
       <c r="H30">
-        <v>-3.339627595333314</v>
+        <v>-3.339627628213829</v>
       </c>
       <c r="I30">
-        <v>0.0008389080314615653</v>
+        <v>0.000838907932147434</v>
       </c>
       <c r="J30">
-        <v>0.008221192785592095</v>
+        <v>0.008221191812326147</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1956,6 +2101,11 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>solute carrier family 22 member 10 [Source:HGNC Symbol;Acc:HGNC:18057]</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -1982,19 +2132,19 @@
         <v>840.4746725251482</v>
       </c>
       <c r="F31">
-        <v>-3.208452666811003</v>
+        <v>-3.208452663910399</v>
       </c>
       <c r="G31">
-        <v>0.7198284462018584</v>
+        <v>0.719828438714218</v>
       </c>
       <c r="H31">
-        <v>-4.457246283805892</v>
+        <v>-4.457246326140499</v>
       </c>
       <c r="I31">
-        <v>8.301920492115536E-06</v>
+        <v>8.301918853180774E-06</v>
       </c>
       <c r="J31">
-        <v>0.0001782444146599024</v>
+        <v>0.0001782443794715424</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2009,6 +2159,11 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>major histocompatibility complex, class II, DR beta 5 [Source:HGNC Symbol;Acc:HGNC:4953]</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2035,19 +2190,19 @@
         <v>1252.617269587523</v>
       </c>
       <c r="F32">
-        <v>-4.051154838342162</v>
+        <v>-4.051154837967569</v>
       </c>
       <c r="G32">
-        <v>0.6694915622009934</v>
+        <v>0.6694915569562662</v>
       </c>
       <c r="H32">
-        <v>-6.051091704612004</v>
+        <v>-6.051091751456108</v>
       </c>
       <c r="I32">
-        <v>1.438675166393387E-09</v>
+        <v>1.438674747990799E-09</v>
       </c>
       <c r="J32">
-        <v>1.116627730396227E-07</v>
+        <v>1.116627405653058E-07</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2062,6 +2217,11 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>AE binding protein 1 [Source:HGNC Symbol;Acc:HGNC:303]</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2088,19 +2248,19 @@
         <v>160.1769332457739</v>
       </c>
       <c r="F33">
-        <v>-2.456508453881568</v>
+        <v>-2.45650845403602</v>
       </c>
       <c r="G33">
-        <v>0.508340551939453</v>
+        <v>0.5083405535877205</v>
       </c>
       <c r="H33">
-        <v>-4.832407024207181</v>
+        <v>-4.832407008842192</v>
       </c>
       <c r="I33">
-        <v>1.348921141467333E-06</v>
+        <v>1.348921245606892E-06</v>
       </c>
       <c r="J33">
-        <v>3.759300337342442E-05</v>
+        <v>3.759300627568364E-05</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2115,6 +2275,11 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>protein phosphatase 1 regulatory inhibitor subunit 14A [Source:HGNC Symbol;Acc:HGNC:14871]</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2141,19 +2306,19 @@
         <v>962.4172735633736</v>
       </c>
       <c r="F34">
-        <v>-2.649185001563941</v>
+        <v>-2.649185001488624</v>
       </c>
       <c r="G34">
-        <v>0.5605548847389187</v>
+        <v>0.5605548824419596</v>
       </c>
       <c r="H34">
-        <v>-4.726004667317835</v>
+        <v>-4.726004686548999</v>
       </c>
       <c r="I34">
-        <v>2.289803873330287E-06</v>
+        <v>2.289803656591873E-06</v>
       </c>
       <c r="J34">
-        <v>5.994034658635082E-05</v>
+        <v>5.994034091277513E-05</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2168,6 +2333,11 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>quiescin sulfhydryl oxidase 1 [Source:HGNC Symbol;Acc:HGNC:9756]</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2194,19 +2364,19 @@
         <v>485.7529324115034</v>
       </c>
       <c r="F35">
-        <v>-3.282713315286387</v>
+        <v>-3.282713314828378</v>
       </c>
       <c r="G35">
-        <v>0.6850040823246777</v>
+        <v>0.6850040771221914</v>
       </c>
       <c r="H35">
-        <v>-4.792253652191301</v>
+        <v>-4.792253687919008</v>
       </c>
       <c r="I35">
-        <v>1.649182114035367E-06</v>
+        <v>1.649181820265093E-06</v>
       </c>
       <c r="J35">
-        <v>4.475568873456468E-05</v>
+        <v>4.475568076219413E-05</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2221,6 +2391,11 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>thrombospondin 2 [Source:HGNC Symbol;Acc:HGNC:11786]</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2247,19 +2422,19 @@
         <v>630.91648500881</v>
       </c>
       <c r="F36">
-        <v>-2.236694059218286</v>
+        <v>-2.236694059231398</v>
       </c>
       <c r="G36">
-        <v>0.4663601430229229</v>
+        <v>0.4663601438221885</v>
       </c>
       <c r="H36">
-        <v>-4.796066071856287</v>
+        <v>-4.796066063664723</v>
       </c>
       <c r="I36">
-        <v>1.618119275640109E-06</v>
+        <v>1.618119341775179E-06</v>
       </c>
       <c r="J36">
-        <v>4.398960685772576E-05</v>
+        <v>4.398960865564992E-05</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2274,6 +2449,11 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>collagen type V alpha 1 chain [Source:HGNC Symbol;Acc:HGNC:2209]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2300,19 +2480,19 @@
         <v>1029.136170728543</v>
       </c>
       <c r="F37">
-        <v>-1.893386840042929</v>
+        <v>-1.893386840021924</v>
       </c>
       <c r="G37">
-        <v>0.5541610938147109</v>
+        <v>0.554161091667173</v>
       </c>
       <c r="H37">
-        <v>-3.416672265837561</v>
+        <v>-3.41667227904027</v>
       </c>
       <c r="I37">
-        <v>0.0006339154331541304</v>
+        <v>0.0006339154024142381</v>
       </c>
       <c r="J37">
-        <v>0.00649522724016605</v>
+        <v>0.006495226925198824</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2327,6 +2507,11 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>transmembrane serine protease 2 [Source:HGNC Symbol;Acc:HGNC:11876]</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2353,19 +2538,19 @@
         <v>118.8456394838764</v>
       </c>
       <c r="F38">
-        <v>-2.674280457674093</v>
+        <v>-2.674280456076</v>
       </c>
       <c r="G38">
-        <v>0.760579174773316</v>
+        <v>0.7605791683968134</v>
       </c>
       <c r="H38">
-        <v>-3.516110546244103</v>
+        <v>-3.516110573621128</v>
       </c>
       <c r="I38">
-        <v>0.0004379186072925999</v>
+        <v>0.000437918562135326</v>
       </c>
       <c r="J38">
-        <v>0.004817725401136093</v>
+        <v>0.004817724904342073</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2380,6 +2565,11 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>synaptogyrin 1 [Source:HGNC Symbol;Acc:HGNC:11498]</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2406,19 +2596,19 @@
         <v>680.3332294978711</v>
       </c>
       <c r="F39">
-        <v>-1.910876151406166</v>
+        <v>-1.910876151436208</v>
       </c>
       <c r="G39">
-        <v>0.3480767902547562</v>
+        <v>0.3480767961118761</v>
       </c>
       <c r="H39">
-        <v>-5.48981203259086</v>
+        <v>-5.489811940299605</v>
       </c>
       <c r="I39">
-        <v>4.023617064863248E-08</v>
+        <v>4.023619167234104E-08</v>
       </c>
       <c r="J39">
-        <v>1.951831490558506E-06</v>
+        <v>1.951832510405468E-06</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2433,6 +2623,11 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>small integral membrane protein 19 [Source:HGNC Symbol;Acc:HGNC:25166]</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2459,19 +2654,19 @@
         <v>183.8695127276589</v>
       </c>
       <c r="F40">
-        <v>-4.351010637448264</v>
+        <v>-4.351010637041444</v>
       </c>
       <c r="G40">
-        <v>0.6183980837355366</v>
+        <v>0.6183980816225528</v>
       </c>
       <c r="H40">
-        <v>-7.035938098587335</v>
+        <v>-7.035938121970338</v>
       </c>
       <c r="I40">
-        <v>1.979247977468629E-12</v>
+        <v>1.979247645504614E-12</v>
       </c>
       <c r="J40">
-        <v>2.898477957947691E-10</v>
+        <v>2.898477471808314E-10</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2486,6 +2681,11 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>brain abundant membrane attached signal protein 1 [Source:HGNC Symbol;Acc:HGNC:957]</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2512,19 +2712,19 @@
         <v>524.3763975096505</v>
       </c>
       <c r="F41">
-        <v>-1.591646414404454</v>
+        <v>-1.591646414382204</v>
       </c>
       <c r="G41">
-        <v>0.3644612489444609</v>
+        <v>0.364461254205058</v>
       </c>
       <c r="H41">
-        <v>-4.367121110993615</v>
+        <v>-4.367121047897975</v>
       </c>
       <c r="I41">
-        <v>1.258949265462646E-05</v>
+        <v>1.258949629011075E-05</v>
       </c>
       <c r="J41">
-        <v>0.0002480034193880285</v>
+        <v>0.0002480034910043009</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2539,6 +2739,11 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>6-pyruvoyltetrahydropterin synthase [Source:HGNC Symbol;Acc:HGNC:9689]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2565,19 +2770,19 @@
         <v>955.8558458423207</v>
       </c>
       <c r="F42">
-        <v>-2.549011225429154</v>
+        <v>-2.549011225401938</v>
       </c>
       <c r="G42">
-        <v>0.5573756995123333</v>
+        <v>0.5573756972923067</v>
       </c>
       <c r="H42">
-        <v>-4.573237096018662</v>
+        <v>-4.57323711418503</v>
       </c>
       <c r="I42">
-        <v>4.802461699820493E-06</v>
+        <v>4.802461283255553E-06</v>
       </c>
       <c r="J42">
-        <v>0.0001129336033705667</v>
+        <v>0.000112933623882484</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2592,6 +2797,11 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>TYRO protein tyrosine kinase binding protein [Source:HGNC Symbol;Acc:HGNC:12449]</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2618,19 +2828,19 @@
         <v>3254.243778294501</v>
       </c>
       <c r="F43">
-        <v>-3.340141388400406</v>
+        <v>-3.340141388368614</v>
       </c>
       <c r="G43">
-        <v>0.5756352961652567</v>
+        <v>0.5756352931882612</v>
       </c>
       <c r="H43">
-        <v>-5.802530544342262</v>
+        <v>-5.802530574295803</v>
       </c>
       <c r="I43">
-        <v>6.532148982061912E-09</v>
+        <v>6.53214781477018E-09</v>
       </c>
       <c r="J43">
-        <v>4.072230869419561E-07</v>
+        <v>4.072230141713956E-07</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2645,6 +2855,11 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>complement C1q C chain [Source:HGNC Symbol;Acc:HGNC:1245]</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2671,19 +2886,19 @@
         <v>398.1096338644838</v>
       </c>
       <c r="F44">
-        <v>-2.986301101022261</v>
+        <v>-2.986301100910701</v>
       </c>
       <c r="G44">
-        <v>0.5826609522289137</v>
+        <v>0.5826609499088125</v>
       </c>
       <c r="H44">
-        <v>-5.125280988194683</v>
+        <v>-5.125281008411603</v>
       </c>
       <c r="I44">
-        <v>2.970943343566636E-07</v>
+        <v>2.970943024764212E-07</v>
       </c>
       <c r="J44">
-        <v>1.045758583269499E-05</v>
+        <v>1.045758471052491E-05</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2698,6 +2913,11 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>membrane spanning 4-domains A7 [Source:HGNC Symbol;Acc:HGNC:13378]</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2724,19 +2944,19 @@
         <v>50.63464610097593</v>
       </c>
       <c r="F45">
-        <v>-3.974150387166732</v>
+        <v>-3.974150385866995</v>
       </c>
       <c r="G45">
-        <v>0.7850184764692206</v>
+        <v>0.7850184741627472</v>
       </c>
       <c r="H45">
-        <v>-5.062492802769786</v>
+        <v>-5.062492815988287</v>
       </c>
       <c r="I45">
-        <v>4.138096920965503E-07</v>
+        <v>4.138096633958961E-07</v>
       </c>
       <c r="J45">
-        <v>1.378448036569689E-05</v>
+        <v>1.378447940964484E-05</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2751,6 +2971,11 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>solute carrier family 8 member A1 [Source:HGNC Symbol;Acc:HGNC:11068]</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2777,19 +3002,19 @@
         <v>3474.678112276243</v>
       </c>
       <c r="F46">
-        <v>-3.302730600729213</v>
+        <v>-3.302730600708875</v>
       </c>
       <c r="G46">
-        <v>0.5695862751886459</v>
+        <v>0.5695862723726084</v>
       </c>
       <c r="H46">
-        <v>-5.798472934825115</v>
+        <v>-5.79847296345709</v>
       </c>
       <c r="I46">
-        <v>6.692150079684783E-09</v>
+        <v>6.692148937321692E-09</v>
       </c>
       <c r="J46">
-        <v>4.122311336783606E-07</v>
+        <v>4.122310633097009E-07</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2804,6 +3029,11 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>complement C1q B chain [Source:HGNC Symbol;Acc:HGNC:1242]</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2830,19 +3060,19 @@
         <v>329.3505426410196</v>
       </c>
       <c r="F47">
-        <v>-4.284078931451623</v>
+        <v>-4.284078931135483</v>
       </c>
       <c r="G47">
-        <v>0.5860129282145913</v>
+        <v>0.5860129258089429</v>
       </c>
       <c r="H47">
-        <v>-7.310553616118929</v>
+        <v>-7.310553645590091</v>
       </c>
       <c r="I47">
-        <v>2.660439649805503E-13</v>
+        <v>2.660439066255641E-13</v>
       </c>
       <c r="J47">
-        <v>4.802093567898933E-11</v>
+        <v>4.802092514591432E-11</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2857,6 +3087,11 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>angiopoietin like 6 [Source:HGNC Symbol;Acc:HGNC:23140]</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2883,19 +3118,19 @@
         <v>324.4146662678375</v>
       </c>
       <c r="F48">
-        <v>-2.862763372768859</v>
+        <v>-2.862763372853134</v>
       </c>
       <c r="G48">
-        <v>0.4526615709085902</v>
+        <v>0.4526615730458685</v>
       </c>
       <c r="H48">
-        <v>-6.324290721261518</v>
+        <v>-6.324290691587042</v>
       </c>
       <c r="I48">
-        <v>2.543983730076535E-10</v>
+        <v>2.543984218909265E-10</v>
       </c>
       <c r="J48">
-        <v>2.452811145464475E-08</v>
+        <v>2.452811616778169E-08</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2910,6 +3145,11 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>peroxidasin [Source:HGNC Symbol;Acc:HGNC:14966]</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2936,19 +3176,19 @@
         <v>138.5826518162233</v>
       </c>
       <c r="F49">
-        <v>-4.550703362690687</v>
+        <v>-4.550703361210541</v>
       </c>
       <c r="G49">
-        <v>0.7223466677554171</v>
+        <v>0.72234666233559</v>
       </c>
       <c r="H49">
-        <v>-6.299888358080627</v>
+        <v>-6.299888403300134</v>
       </c>
       <c r="I49">
-        <v>2.978601042527672E-10</v>
+        <v>2.97860017357267E-10</v>
       </c>
       <c r="J49">
-        <v>2.819318535558357E-08</v>
+        <v>2.819317713071253E-08</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2963,6 +3203,11 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>peptidase domain containing associated with muscle regeneration 1 [Source:HGNC Symbol;Acc:HGNC:24554]</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -2989,19 +3234,19 @@
         <v>251740.2878877762</v>
       </c>
       <c r="F50">
-        <v>-2.334089416672241</v>
+        <v>-2.334089416672281</v>
       </c>
       <c r="G50">
-        <v>0.5602247900684179</v>
+        <v>0.5602247874215768</v>
       </c>
       <c r="H50">
-        <v>-4.16634439969568</v>
+        <v>-4.166344419380086</v>
       </c>
       <c r="I50">
-        <v>3.095229866016156E-05</v>
+        <v>3.095229598882799E-05</v>
       </c>
       <c r="J50">
-        <v>0.0005297381831330627</v>
+        <v>0.0005297381374140869</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3016,6 +3261,11 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>fibrinogen alpha chain [Source:HGNC Symbol;Acc:HGNC:3661]</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3042,19 +3292,19 @@
         <v>2155.833137803949</v>
       </c>
       <c r="F51">
-        <v>-2.290211091020964</v>
+        <v>-2.290211091035064</v>
       </c>
       <c r="G51">
-        <v>0.3671046962060929</v>
+        <v>0.3671047003404657</v>
       </c>
       <c r="H51">
-        <v>-6.238577481273184</v>
+        <v>-6.238577411052058</v>
       </c>
       <c r="I51">
-        <v>4.41567896242489E-10</v>
+        <v>4.415680944271891E-10</v>
       </c>
       <c r="J51">
-        <v>3.933539262046106E-08</v>
+        <v>3.933539325377522E-08</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3069,6 +3319,11 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>mitochondrial pyruvate carrier 1 [Source:HGNC Symbol;Acc:HGNC:21606]</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3095,19 +3350,19 @@
         <v>5893.940923325187</v>
       </c>
       <c r="F52">
-        <v>-1.854205623280972</v>
+        <v>-1.854205623281646</v>
       </c>
       <c r="G52">
-        <v>0.4178131455950198</v>
+        <v>0.41781314747212</v>
       </c>
       <c r="H52">
-        <v>-4.437882442976619</v>
+        <v>-4.437882423040253</v>
       </c>
       <c r="I52">
-        <v>9.084821036422699E-06</v>
+        <v>9.084821877652171E-06</v>
       </c>
       <c r="J52">
-        <v>0.0001925065243911178</v>
+        <v>0.0001925064992366755</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3122,6 +3377,11 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>acetyl-CoA acetyltransferase 1 [Source:HGNC Symbol;Acc:HGNC:93]</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3148,19 +3408,19 @@
         <v>275.1617659588272</v>
       </c>
       <c r="F53">
-        <v>-1.353840665066331</v>
+        <v>-1.353840665061993</v>
       </c>
       <c r="G53">
-        <v>0.370688524387388</v>
+        <v>0.370688530628111</v>
       </c>
       <c r="H53">
-        <v>-3.652232470114182</v>
+        <v>-3.652232408615355</v>
       </c>
       <c r="I53">
-        <v>0.0002599703759831866</v>
+        <v>0.0002599704382594993</v>
       </c>
       <c r="J53">
-        <v>0.003194216700760859</v>
+        <v>0.003194216606630954</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3175,6 +3435,11 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>F-box protein 8 [Source:HGNC Symbol;Acc:HGNC:13587]</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3201,19 +3466,19 @@
         <v>5474.078458767509</v>
       </c>
       <c r="F54">
-        <v>-4.425359857851053</v>
+        <v>-4.425359857866413</v>
       </c>
       <c r="G54">
-        <v>0.4598098377827904</v>
+        <v>0.4598098381970281</v>
       </c>
       <c r="H54">
-        <v>-9.624326176208411</v>
+        <v>-9.624326167571365</v>
       </c>
       <c r="I54">
-        <v>6.311924931927916E-22</v>
+        <v>6.311925462159713E-22</v>
       </c>
       <c r="J54">
-        <v>4.082500446596543E-19</v>
+        <v>4.082500789546051E-19</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3228,6 +3493,11 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>lymphocyte antigen 6 family member E [Source:HGNC Symbol;Acc:HGNC:6727]</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3254,19 +3524,19 @@
         <v>5193.055280958887</v>
       </c>
       <c r="F55">
-        <v>-3.103815130899237</v>
+        <v>-3.103815130891967</v>
       </c>
       <c r="G55">
-        <v>0.5440244528748803</v>
+        <v>0.5440244507238342</v>
       </c>
       <c r="H55">
-        <v>-5.705286066641347</v>
+        <v>-5.705286089186406</v>
       </c>
       <c r="I55">
-        <v>1.161478544264719E-08</v>
+        <v>1.161478390525049E-08</v>
       </c>
       <c r="J55">
-        <v>6.580157460810666E-07</v>
+        <v>6.580156589824943E-07</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3281,6 +3551,11 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>fructose-bisphosphatase 1 [Source:HGNC Symbol;Acc:HGNC:3606]</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3307,19 +3582,19 @@
         <v>3008.956758829662</v>
       </c>
       <c r="F56">
-        <v>-1.466979789664135</v>
+        <v>-1.466979789666891</v>
       </c>
       <c r="G56">
-        <v>0.3791194657331753</v>
+        <v>0.3791194692331612</v>
       </c>
       <c r="H56">
-        <v>-3.869439377973265</v>
+        <v>-3.86943934225833</v>
       </c>
       <c r="I56">
-        <v>0.0001090859000858335</v>
+        <v>0.0001090859160644664</v>
       </c>
       <c r="J56">
-        <v>0.001552099383164431</v>
+        <v>0.001552099610512109</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3334,6 +3609,11 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>hydroxyacyl-CoA dehydrogenase trifunctional multienzyme complex subunit beta [Source:HGNC Symbol;Acc:HGNC:4803]</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3360,19 +3640,19 @@
         <v>34.59696890829428</v>
       </c>
       <c r="F57">
-        <v>-6.386663889999043</v>
+        <v>-6.386663882617527</v>
       </c>
       <c r="G57">
-        <v>1.048341134564228</v>
+        <v>1.04834112985003</v>
       </c>
       <c r="H57">
-        <v>-6.092161873104253</v>
+        <v>-6.092161893458446</v>
       </c>
       <c r="I57">
-        <v>1.113959565796329E-09</v>
+        <v>1.113959424120265E-09</v>
       </c>
       <c r="J57">
-        <v>8.867689405054574E-08</v>
+        <v>8.86768827724045E-08</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3387,6 +3667,11 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>kinesin family member 19 [Source:HGNC Symbol;Acc:HGNC:26735]</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3413,19 +3698,19 @@
         <v>1957.096437933865</v>
       </c>
       <c r="F58">
-        <v>-1.653903142853158</v>
+        <v>-1.653903142856723</v>
       </c>
       <c r="G58">
-        <v>0.380074440210685</v>
+        <v>0.3800744437831033</v>
       </c>
       <c r="H58">
-        <v>-4.351524248608659</v>
+        <v>-4.351524207716935</v>
       </c>
       <c r="I58">
-        <v>1.3519436619914E-05</v>
+        <v>1.35194391418077E-05</v>
       </c>
       <c r="J58">
-        <v>0.0002636459983051822</v>
+        <v>0.0002636460474852775</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3440,6 +3725,11 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>kallikrein B1 [Source:HGNC Symbol;Acc:HGNC:6371]</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3466,19 +3756,19 @@
         <v>3844.480692131042</v>
       </c>
       <c r="F59">
-        <v>-2.084354545266425</v>
+        <v>-2.084354545269317</v>
       </c>
       <c r="G59">
-        <v>0.3814966789045593</v>
+        <v>0.3814966822616386</v>
       </c>
       <c r="H59">
-        <v>-5.463624352514683</v>
+        <v>-5.46362430444368</v>
       </c>
       <c r="I59">
-        <v>4.665102018354224E-08</v>
+        <v>4.665103282274022E-08</v>
       </c>
       <c r="J59">
-        <v>2.187806000933916E-06</v>
+        <v>2.187806593677935E-06</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3493,6 +3783,11 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>lecithin-cholesterol acyltransferase [Source:HGNC Symbol;Acc:HGNC:6522]</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3519,19 +3814,19 @@
         <v>1194.87053909427</v>
       </c>
       <c r="F60">
-        <v>-2.470256121612741</v>
+        <v>-2.470256121593862</v>
       </c>
       <c r="G60">
-        <v>0.5905556353988938</v>
+        <v>0.5905556322266301</v>
       </c>
       <c r="H60">
-        <v>-4.182935482351623</v>
+        <v>-4.18293550478896</v>
       </c>
       <c r="I60">
-        <v>2.877690775817133E-05</v>
+        <v>2.87769049170022E-05</v>
       </c>
       <c r="J60">
-        <v>0.0004952371830710572</v>
+        <v>0.0004952371341758595</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3546,6 +3841,11 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>growth hormone receptor [Source:HGNC Symbol;Acc:HGNC:4263]</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3572,19 +3872,19 @@
         <v>125.7966156250244</v>
       </c>
       <c r="F61">
-        <v>-3.05895183674253</v>
+        <v>-3.058951836865878</v>
       </c>
       <c r="G61">
-        <v>0.5261002315808265</v>
+        <v>0.5261002335022857</v>
       </c>
       <c r="H61">
-        <v>-5.81438983128935</v>
+        <v>-5.814389810288096</v>
       </c>
       <c r="I61">
-        <v>6.085544793704227E-09</v>
+        <v>6.085545557646436E-09</v>
       </c>
       <c r="J61">
-        <v>3.840077716775233E-07</v>
+        <v>3.840078198835188E-07</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3599,6 +3899,11 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>adrenoceptor alpha 2B [Source:HGNC Symbol;Acc:HGNC:282]</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3625,19 +3930,19 @@
         <v>251.8328329508469</v>
       </c>
       <c r="F62">
-        <v>-3.885815211463782</v>
+        <v>-3.885815210576796</v>
       </c>
       <c r="G62">
-        <v>0.6957048728606762</v>
+        <v>0.695704866747292</v>
       </c>
       <c r="H62">
-        <v>-5.585436243224311</v>
+        <v>-5.585436291030404</v>
       </c>
       <c r="I62">
-        <v>2.331142997260073E-08</v>
+        <v>2.33114235596266E-08</v>
       </c>
       <c r="J62">
-        <v>1.206211091548937E-06</v>
+        <v>1.206210759720279E-06</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3652,6 +3957,11 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>aminoadipate aminotransferase [Source:HGNC Symbol;Acc:HGNC:17929]</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3678,19 +3988,19 @@
         <v>654.5984844908767</v>
       </c>
       <c r="F63">
-        <v>-1.895957324716788</v>
+        <v>-1.89595732472671</v>
       </c>
       <c r="G63">
-        <v>0.4041701770244326</v>
+        <v>0.4041701801857944</v>
       </c>
       <c r="H63">
-        <v>-4.690987689084675</v>
+        <v>-4.690987652416986</v>
       </c>
       <c r="I63">
-        <v>2.718893324126089E-06</v>
+        <v>2.718893811451702E-06</v>
       </c>
       <c r="J63">
-        <v>6.967964838742972E-05</v>
+        <v>6.96796483874282E-05</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3705,6 +4015,11 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>methionine sulfoxide reductase A [Source:HGNC Symbol;Acc:HGNC:7377]</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3731,19 +4046,19 @@
         <v>1836.62705697003</v>
       </c>
       <c r="F64">
-        <v>-2.599742656839103</v>
+        <v>-2.599742656886944</v>
       </c>
       <c r="G64">
-        <v>0.4371816245482492</v>
+        <v>0.4371816261180591</v>
       </c>
       <c r="H64">
-        <v>-5.946596359180198</v>
+        <v>-5.946596337936888</v>
       </c>
       <c r="I64">
-        <v>2.737753981221184E-09</v>
+        <v>2.737754336361316E-09</v>
       </c>
       <c r="J64">
-        <v>1.95844032490767E-07</v>
+        <v>1.958440578955609E-07</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3758,6 +4073,11 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>aldehyde dehydrogenase 8 family member A1 [Source:HGNC Symbol;Acc:HGNC:15471]</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3784,19 +4104,19 @@
         <v>1005.73860527775</v>
       </c>
       <c r="F65">
-        <v>-3.973317012257473</v>
+        <v>-3.973317012251531</v>
       </c>
       <c r="G65">
-        <v>0.4229191611674161</v>
+        <v>0.4229191634378963</v>
       </c>
       <c r="H65">
-        <v>-9.39497988525661</v>
+        <v>-9.394979834804751</v>
       </c>
       <c r="I65">
-        <v>5.722875700298628E-21</v>
+        <v>5.722878442981638E-21</v>
       </c>
       <c r="J65">
-        <v>3.416776903682139E-18</v>
+        <v>3.416778541169384E-18</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3811,6 +4131,11 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>lysine demethylase 8 [Source:HGNC Symbol;Acc:HGNC:25840]</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3837,19 +4162,19 @@
         <v>2904.936865999297</v>
       </c>
       <c r="F66">
-        <v>-2.312683586656236</v>
+        <v>-2.31268358665773</v>
       </c>
       <c r="G66">
-        <v>0.460613089070846</v>
+        <v>0.4606130894896764</v>
       </c>
       <c r="H66">
-        <v>-5.020881172355322</v>
+        <v>-5.020881167793134</v>
       </c>
       <c r="I66">
-        <v>5.143497288446873E-07</v>
+        <v>5.143497410625335E-07</v>
       </c>
       <c r="J66">
-        <v>1.642849967254338E-05</v>
+        <v>1.642850006278541E-05</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3864,6 +4189,11 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>hydroxyacid oxidase 1 [Source:HGNC Symbol;Acc:HGNC:4809]</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3890,19 +4220,19 @@
         <v>1717.356614255247</v>
       </c>
       <c r="F67">
-        <v>-4.412981137926344</v>
+        <v>-4.41298113785442</v>
       </c>
       <c r="G67">
-        <v>0.7057419561535752</v>
+        <v>0.7057419501856724</v>
       </c>
       <c r="H67">
-        <v>-6.25296696540179</v>
+        <v>-6.252967018176284</v>
       </c>
       <c r="I67">
-        <v>4.027273494463507E-10</v>
+        <v>4.027272133035429E-10</v>
       </c>
       <c r="J67">
-        <v>3.634614328753315E-08</v>
+        <v>3.634613100064475E-08</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3917,6 +4247,11 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>urocanate hydratase 1 [Source:HGNC Symbol;Acc:HGNC:26444]</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3943,19 +4278,19 @@
         <v>906.0813255247951</v>
       </c>
       <c r="F68">
-        <v>-1.994752819860426</v>
+        <v>-1.994752819862476</v>
       </c>
       <c r="G68">
-        <v>0.4742263729021637</v>
+        <v>0.4742263732073485</v>
       </c>
       <c r="H68">
-        <v>-4.206330423280692</v>
+        <v>-4.206330420578063</v>
       </c>
       <c r="I68">
-        <v>2.595506725722276E-05</v>
+        <v>2.595506756745964E-05</v>
       </c>
       <c r="J68">
-        <v>0.0004547409808508678</v>
+        <v>0.000454740986286316</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3970,6 +4305,11 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>acyl-CoA thioesterase 2 [Source:HGNC Symbol;Acc:HGNC:18431]</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -3996,19 +4336,19 @@
         <v>11020.06495861616</v>
       </c>
       <c r="F69">
-        <v>-1.857775933404505</v>
+        <v>-1.857775933404216</v>
       </c>
       <c r="G69">
-        <v>0.4879190967276607</v>
+        <v>0.4879190961939843</v>
       </c>
       <c r="H69">
-        <v>-3.807549132354314</v>
+        <v>-3.807549136518344</v>
       </c>
       <c r="I69">
-        <v>0.0001403508605526205</v>
+        <v>0.0001403508581900928</v>
       </c>
       <c r="J69">
-        <v>0.001926318663446797</v>
+        <v>0.001926318631021053</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4023,6 +4363,11 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>enoyl-CoA hydratase, short chain 1 [Source:HGNC Symbol;Acc:HGNC:3151]</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4049,19 +4394,19 @@
         <v>24.02747357167125</v>
       </c>
       <c r="F70">
-        <v>-6.211963196000767</v>
+        <v>-6.211963191152858</v>
       </c>
       <c r="G70">
-        <v>1.184207697261679</v>
+        <v>1.184207692014238</v>
       </c>
       <c r="H70">
-        <v>-5.245670341752628</v>
+        <v>-5.245670360903355</v>
       </c>
       <c r="I70">
-        <v>1.55715113112193E-07</v>
+        <v>1.55715096936153E-07</v>
       </c>
       <c r="J70">
-        <v>6.088578591537964E-06</v>
+        <v>6.088577959042578E-06</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -4076,6 +4421,11 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>potassium two pore domain channel subfamily K member 17 [Source:HGNC Symbol;Acc:HGNC:14465]</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4102,19 +4452,19 @@
         <v>380.1093379362186</v>
       </c>
       <c r="F71">
-        <v>-5.168125034938406</v>
+        <v>-5.168125033251806</v>
       </c>
       <c r="G71">
-        <v>0.6083862518978047</v>
+        <v>0.6083862489064819</v>
       </c>
       <c r="H71">
-        <v>-8.494809044117806</v>
+        <v>-8.494809083112964</v>
       </c>
       <c r="I71">
-        <v>1.982585928519041E-17</v>
+        <v>1.982585262910194E-17</v>
       </c>
       <c r="J71">
-        <v>7.327543182952636E-15</v>
+        <v>7.327540722894032E-15</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -4129,6 +4479,11 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>N-acetyltransferase 2 [Source:HGNC Symbol;Acc:HGNC:7646]</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4155,19 +4510,19 @@
         <v>4806.763583322518</v>
       </c>
       <c r="F72">
-        <v>-1.84038044316409</v>
+        <v>-1.840380443164185</v>
       </c>
       <c r="G72">
-        <v>0.4369083683927866</v>
+        <v>0.4369083695652696</v>
       </c>
       <c r="H72">
-        <v>-4.212280139961894</v>
+        <v>-4.21228012865808</v>
       </c>
       <c r="I72">
-        <v>2.528057379094103E-05</v>
+        <v>2.528057505642194E-05</v>
       </c>
       <c r="J72">
-        <v>0.0004449323661641468</v>
+        <v>0.0004449323884363241</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4182,6 +4537,11 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>acetyl-CoA acyltransferase 1 [Source:HGNC Symbol;Acc:HGNC:82]</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4208,19 +4568,19 @@
         <v>1093.296805790114</v>
       </c>
       <c r="F73">
-        <v>-1.82108462265651</v>
+        <v>-1.821084622658252</v>
       </c>
       <c r="G73">
-        <v>0.3737819713968607</v>
+        <v>0.3737819755180711</v>
       </c>
       <c r="H73">
-        <v>-4.87205045190097</v>
+        <v>-4.872050398187832</v>
       </c>
       <c r="I73">
-        <v>1.104459544252868E-06</v>
+        <v>1.104459844600074E-06</v>
       </c>
       <c r="J73">
-        <v>3.159547737065872E-05</v>
+        <v>3.159547737065944E-05</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4235,6 +4595,11 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>electron transfer flavoprotein dehydrogenase [Source:HGNC Symbol;Acc:HGNC:3483]</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4261,19 +4626,19 @@
         <v>217.9066863560347</v>
       </c>
       <c r="F74">
-        <v>-3.500670161339246</v>
+        <v>-3.500670160864403</v>
       </c>
       <c r="G74">
-        <v>0.7224472065492891</v>
+        <v>0.7224472006821048</v>
       </c>
       <c r="H74">
-        <v>-4.845572284873127</v>
+        <v>-4.845572323568027</v>
       </c>
       <c r="I74">
-        <v>1.262472349665151E-06</v>
+        <v>1.262472103588875E-06</v>
       </c>
       <c r="J74">
-        <v>3.550246065915243E-05</v>
+        <v>3.550245373914875E-05</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4288,6 +4653,11 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>Rho GTPase activating protein 10 [Source:HGNC Symbol;Acc:HGNC:26099]</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4314,19 +4684,19 @@
         <v>3343.025048236378</v>
       </c>
       <c r="F75">
-        <v>-3.882854229251635</v>
+        <v>-3.882854229268908</v>
       </c>
       <c r="G75">
-        <v>0.4542427013444494</v>
+        <v>0.4542427020085772</v>
       </c>
       <c r="H75">
-        <v>-8.547972741794899</v>
+        <v>-8.547972729335319</v>
       </c>
       <c r="I75">
-        <v>1.252692920907198E-17</v>
+        <v>1.252693056103268E-17</v>
       </c>
       <c r="J75">
-        <v>4.742817612498156E-15</v>
+        <v>4.742818124363666E-15</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4341,6 +4711,11 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>tryptophan 2,3-dioxygenase [Source:HGNC Symbol;Acc:HGNC:11708]</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4367,19 +4742,19 @@
         <v>12267.17686820691</v>
       </c>
       <c r="F76">
-        <v>-9.849871125899588</v>
+        <v>-9.849871124804926</v>
       </c>
       <c r="G76">
-        <v>0.6554810045295579</v>
+        <v>0.6554809982832243</v>
       </c>
       <c r="H76">
-        <v>-15.02693603298068</v>
+        <v>-15.02693617450819</v>
       </c>
       <c r="I76">
-        <v>4.8911148342742E-51</v>
+        <v>4.891104386563279E-51</v>
       </c>
       <c r="J76">
-        <v>2.530825852414613E-47</v>
+        <v>2.530820446420726E-47</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4394,6 +4769,11 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>metallothionein 1G [Source:HGNC Symbol;Acc:HGNC:7399]</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4420,19 +4800,19 @@
         <v>44505.75316832173</v>
       </c>
       <c r="F77">
-        <v>-1.218848702464483</v>
+        <v>-1.218848702464077</v>
       </c>
       <c r="G77">
-        <v>0.3439167927839133</v>
+        <v>0.3439167977334432</v>
       </c>
       <c r="H77">
-        <v>-3.544022065913772</v>
+        <v>-3.544022014908268</v>
       </c>
       <c r="I77">
-        <v>0.0003940722625093981</v>
+        <v>0.0003940723387467381</v>
       </c>
       <c r="J77">
-        <v>0.004445627711434147</v>
+        <v>0.004445628571486639</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4447,6 +4827,11 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>alanine--glyoxylate and serine--pyruvate aminotransferase [Source:HGNC Symbol;Acc:HGNC:341]</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4473,19 +4858,19 @@
         <v>1189.607441143518</v>
       </c>
       <c r="F78">
-        <v>-1.553680327078316</v>
+        <v>-1.553680327087171</v>
       </c>
       <c r="G78">
-        <v>0.4445727650298963</v>
+        <v>0.4445727662539222</v>
       </c>
       <c r="H78">
-        <v>-3.494771720831427</v>
+        <v>-3.494771711229318</v>
       </c>
       <c r="I78">
-        <v>0.0004744673764807303</v>
+        <v>0.000474467393549184</v>
       </c>
       <c r="J78">
-        <v>0.005146860297072241</v>
+        <v>0.005146860482225006</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4500,6 +4885,11 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>acyl-CoA dehydrogenase medium chain [Source:HGNC Symbol;Acc:HGNC:89]</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4526,19 +4916,19 @@
         <v>2625.583695116101</v>
       </c>
       <c r="F79">
-        <v>-1.154725189042973</v>
+        <v>-1.154725189037737</v>
       </c>
       <c r="G79">
-        <v>0.3495296942628496</v>
+        <v>0.3495296991907293</v>
       </c>
       <c r="H79">
-        <v>-3.30365404712828</v>
+        <v>-3.303654000536401</v>
       </c>
       <c r="I79">
-        <v>0.0009543352116896315</v>
+        <v>0.0009543353702801051</v>
       </c>
       <c r="J79">
-        <v>0.009049569634122265</v>
+        <v>0.009049571137970723</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4553,6 +4943,11 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>lactate dehydrogenase D [Source:HGNC Symbol;Acc:HGNC:19708]</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4579,19 +4974,19 @@
         <v>22853.38638797822</v>
       </c>
       <c r="F80">
-        <v>-1.714042792089502</v>
+        <v>-1.714042792089934</v>
       </c>
       <c r="G80">
-        <v>0.4306167416607327</v>
+        <v>0.4306167429833969</v>
       </c>
       <c r="H80">
-        <v>-3.980436955328444</v>
+        <v>-3.980436943103306</v>
       </c>
       <c r="I80">
-        <v>6.878870709839463E-05</v>
+        <v>6.87887106362445E-05</v>
       </c>
       <c r="J80">
-        <v>0.001045844368548854</v>
+        <v>0.001045844422337339</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4606,6 +5001,11 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>insulin like growth factor binding protein 4 [Source:HGNC Symbol;Acc:HGNC:5473]</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4632,19 +5032,19 @@
         <v>11057.6919651623</v>
       </c>
       <c r="F81">
-        <v>-2.655318393367389</v>
+        <v>-2.655318393362673</v>
       </c>
       <c r="G81">
-        <v>0.5834779598601659</v>
+        <v>0.5834779566234731</v>
       </c>
       <c r="H81">
-        <v>-4.550846091947933</v>
+        <v>-4.55084611718449</v>
       </c>
       <c r="I81">
-        <v>5.343062198853537E-06</v>
+        <v>5.343061557928384E-06</v>
       </c>
       <c r="J81">
-        <v>0.0001226928321195317</v>
+        <v>0.0001226928174019561</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4659,6 +5059,11 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>apolipoprotein A5 [Source:HGNC Symbol;Acc:HGNC:17288]</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4685,19 +5090,19 @@
         <v>3497.232484376388</v>
       </c>
       <c r="F82">
-        <v>-1.762873100942517</v>
+        <v>-1.762873100939702</v>
       </c>
       <c r="G82">
-        <v>0.3854997751786574</v>
+        <v>0.3854997783849331</v>
       </c>
       <c r="H82">
-        <v>-4.57295493914497</v>
+        <v>-4.572954901103524</v>
       </c>
       <c r="I82">
-        <v>4.808935890481517E-06</v>
+        <v>4.808936763919469E-06</v>
       </c>
       <c r="J82">
-        <v>0.0001129336033705667</v>
+        <v>0.000112933623882484</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4712,6 +5117,11 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>acyl-CoA dehydrogenase short chain [Source:HGNC Symbol;Acc:HGNC:90]</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4738,19 +5148,19 @@
         <v>48.37800182998918</v>
       </c>
       <c r="F83">
-        <v>-3.286705034496951</v>
+        <v>-3.286705037342241</v>
       </c>
       <c r="G83">
-        <v>0.5776640480313638</v>
+        <v>0.5776640557266191</v>
       </c>
       <c r="H83">
-        <v>-5.689647894304306</v>
+        <v>-5.689647823436122</v>
       </c>
       <c r="I83">
-        <v>1.273015928466431E-08</v>
+        <v>1.27301645676659E-08</v>
       </c>
       <c r="J83">
-        <v>7.05750937770872E-07</v>
+        <v>7.057512306567061E-07</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4765,6 +5175,11 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>pleckstrin and Sec7 domain containing [Source:HGNC Symbol;Acc:HGNC:9507]</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4791,19 +5206,19 @@
         <v>1009.553539381677</v>
       </c>
       <c r="F84">
-        <v>-5.297264083712598</v>
+        <v>-5.297264082587664</v>
       </c>
       <c r="G84">
-        <v>0.7475516057779312</v>
+        <v>0.7475515986745029</v>
       </c>
       <c r="H84">
-        <v>-7.086151702129058</v>
+        <v>-7.086151767958676</v>
       </c>
       <c r="I84">
-        <v>1.37892651876888E-12</v>
+        <v>1.378925863184895E-12</v>
       </c>
       <c r="J84">
-        <v>2.119314490183101E-10</v>
+        <v>2.119313482595952E-10</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4818,6 +5233,11 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>butyrylcholinesterase [Source:HGNC Symbol;Acc:HGNC:983]</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4844,19 +5264,19 @@
         <v>952.2953137517044</v>
       </c>
       <c r="F85">
-        <v>-1.52415165666797</v>
+        <v>-1.524151656719159</v>
       </c>
       <c r="G85">
-        <v>0.4001071313351515</v>
+        <v>0.4001071343910368</v>
       </c>
       <c r="H85">
-        <v>-3.809358887410726</v>
+        <v>-3.809358858444046</v>
       </c>
       <c r="I85">
-        <v>0.0001393275977943337</v>
+        <v>0.0001393276141161496</v>
       </c>
       <c r="J85">
-        <v>0.001915661913694811</v>
+        <v>0.001915662138108938</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4871,6 +5291,11 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>OCIA domain containing 2 [Source:HGNC Symbol;Acc:HGNC:28685]</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4897,19 +5322,19 @@
         <v>911.0212134563229</v>
       </c>
       <c r="F86">
-        <v>-4.168588288998899</v>
+        <v>-4.168588288046</v>
       </c>
       <c r="G86">
-        <v>0.6819438055922875</v>
+        <v>0.6819438000513904</v>
       </c>
       <c r="H86">
-        <v>-6.112803217529577</v>
+        <v>-6.112803265799704</v>
       </c>
       <c r="I86">
-        <v>9.789605863728009E-10</v>
+        <v>9.78960290151848E-10</v>
       </c>
       <c r="J86">
-        <v>7.914794365763014E-08</v>
+        <v>7.914791970847466E-08</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4924,6 +5349,11 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>15-hydroxyprostaglandin dehydrogenase [Source:HGNC Symbol;Acc:HGNC:5154]</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -4950,19 +5380,19 @@
         <v>147.2068730693277</v>
       </c>
       <c r="F87">
-        <v>-2.611995112048884</v>
+        <v>-2.6119951125076</v>
       </c>
       <c r="G87">
-        <v>0.510789168247316</v>
+        <v>0.5107891702120689</v>
       </c>
       <c r="H87">
-        <v>-5.113646244714801</v>
+        <v>-5.113646225943189</v>
       </c>
       <c r="I87">
-        <v>3.159988964830073E-07</v>
+        <v>3.15998927900853E-07</v>
       </c>
       <c r="J87">
-        <v>1.107280106118673E-05</v>
+        <v>1.10728021620879E-05</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4977,6 +5407,11 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>zinc finger protein 397 (ZNF397) pseudogene</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5003,19 +5438,19 @@
         <v>1352.33754953482</v>
       </c>
       <c r="F88">
-        <v>-1.335943147223526</v>
+        <v>-1.335943147225831</v>
       </c>
       <c r="G88">
-        <v>0.3626177953483876</v>
+        <v>0.3626177998759748</v>
       </c>
       <c r="H88">
-        <v>-3.684163227400381</v>
+        <v>-3.684163181406869</v>
       </c>
       <c r="I88">
-        <v>0.0002294551741030121</v>
+        <v>0.000229455215530102</v>
       </c>
       <c r="J88">
-        <v>0.002886412210373628</v>
+        <v>0.002886412731502248</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -5030,6 +5465,11 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>dehydrogenase/reductase 1 [Source:HGNC Symbol;Acc:HGNC:16445]</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5056,19 +5496,19 @@
         <v>398.9647979119754</v>
       </c>
       <c r="F89">
-        <v>-1.521040292496527</v>
+        <v>-1.521040292571744</v>
       </c>
       <c r="G89">
-        <v>0.4091149903612844</v>
+        <v>0.4091149939074558</v>
       </c>
       <c r="H89">
-        <v>-3.717879638566446</v>
+        <v>-3.717879606524057</v>
       </c>
       <c r="I89">
-        <v>0.0002009019422059262</v>
+        <v>0.0002009019676812216</v>
       </c>
       <c r="J89">
-        <v>0.002598834040718827</v>
+        <v>0.002598834370263003</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -5083,6 +5523,11 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>interferon regulatory factor 2 binding protein like [Source:HGNC Symbol;Acc:HGNC:14282]</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5109,19 +5554,19 @@
         <v>616.765560378285</v>
       </c>
       <c r="F90">
-        <v>-3.673729055653777</v>
+        <v>-3.673729053216926</v>
       </c>
       <c r="G90">
-        <v>0.7050490351733625</v>
+        <v>0.705049028126927</v>
       </c>
       <c r="H90">
-        <v>-5.210600784313469</v>
+        <v>-5.210600832933223</v>
       </c>
       <c r="I90">
-        <v>1.882300934700287E-07</v>
+        <v>1.882300441382372E-07</v>
       </c>
       <c r="J90">
-        <v>7.179105014582939E-06</v>
+        <v>7.179103133065987E-06</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -5136,6 +5581,11 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>arginine vasopressin receptor 1A [Source:HGNC Symbol;Acc:HGNC:895]</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5162,19 +5612,19 @@
         <v>356.3616681464908</v>
       </c>
       <c r="F91">
-        <v>-2.764082845068571</v>
+        <v>-2.764082844063091</v>
       </c>
       <c r="G91">
-        <v>0.734302958422862</v>
+        <v>0.7343029507985674</v>
       </c>
       <c r="H91">
-        <v>-3.764226758673663</v>
+        <v>-3.764226796388469</v>
       </c>
       <c r="I91">
-        <v>0.0001670652327834917</v>
+        <v>0.0001670652075716178</v>
       </c>
       <c r="J91">
-        <v>0.002212759051619575</v>
+        <v>0.002212758717691317</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -5189,6 +5639,11 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>reticulophagy regulator 1 [Source:HGNC Symbol;Acc:HGNC:25964]</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5215,19 +5670,19 @@
         <v>18.74288101458379</v>
       </c>
       <c r="F92">
-        <v>-4.098413833530265</v>
+        <v>-4.098413826363311</v>
       </c>
       <c r="G92">
-        <v>1.238861787744101</v>
+        <v>1.238861781743856</v>
       </c>
       <c r="H92">
-        <v>-3.308209094892862</v>
+        <v>-3.308209105130575</v>
       </c>
       <c r="I92">
-        <v>0.0009389467690299857</v>
+        <v>0.0009389467347034583</v>
       </c>
       <c r="J92">
-        <v>0.008925456641550807</v>
+        <v>0.008925456315249101</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5242,6 +5697,11 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>novel transcript</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5268,19 +5728,19 @@
         <v>1648.692543788393</v>
       </c>
       <c r="F93">
-        <v>-4.753021183477965</v>
+        <v>-4.753021182729821</v>
       </c>
       <c r="G93">
-        <v>0.813301451051499</v>
+        <v>0.8133014425144971</v>
       </c>
       <c r="H93">
-        <v>-5.844107590528569</v>
+        <v>-5.844107650952677</v>
       </c>
       <c r="I93">
-        <v>5.092910527848296E-09</v>
+        <v>5.092908679466744E-09</v>
       </c>
       <c r="J93">
-        <v>3.321733198478534E-07</v>
+        <v>3.321731992914381E-07</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5295,6 +5755,11 @@
       <c r="M93" t="inlineStr">
         <is>
           <t>long intergenic non-protein coding RNA 1554 [Source:HGNC Symbol;Acc:HGNC:24687]</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5321,19 +5786,19 @@
         <v>1882.940709812582</v>
       </c>
       <c r="F94">
-        <v>-1.191398699728967</v>
+        <v>-1.191398699745613</v>
       </c>
       <c r="G94">
-        <v>0.3411452232353104</v>
+        <v>0.3411452287324057</v>
       </c>
       <c r="H94">
-        <v>-3.492350525767673</v>
+        <v>-3.492350469541952</v>
       </c>
       <c r="I94">
-        <v>0.0004787894844901937</v>
+        <v>0.0004787895852845397</v>
       </c>
       <c r="J94">
-        <v>0.00517926771271169</v>
+        <v>0.005179268803046626</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5348,6 +5813,11 @@
       <c r="M94" t="inlineStr">
         <is>
           <t>abhydrolase domain containing 2 [Source:HGNC Symbol;Acc:HGNC:18717]</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5374,19 +5844,19 @@
         <v>828.0872066180027</v>
       </c>
       <c r="F95">
-        <v>-1.635865832466167</v>
+        <v>-1.635865832508861</v>
       </c>
       <c r="G95">
-        <v>0.4283650560282679</v>
+        <v>0.4283650580303517</v>
       </c>
       <c r="H95">
-        <v>-3.818859193683192</v>
+        <v>-3.818859175934355</v>
       </c>
       <c r="I95">
-        <v>0.0001340702586979428</v>
+        <v>0.0001340702683429577</v>
       </c>
       <c r="J95">
-        <v>0.001853225846632383</v>
+        <v>0.001853225979953457</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5401,6 +5871,11 @@
       <c r="M95" t="inlineStr">
         <is>
           <t>solute carrier family 46 member 3 [Source:HGNC Symbol;Acc:HGNC:27501]</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5427,19 +5902,19 @@
         <v>950.5980656913133</v>
       </c>
       <c r="F96">
-        <v>1.277494341970162</v>
+        <v>1.277494341989086</v>
       </c>
       <c r="G96">
-        <v>0.3208135903100862</v>
+        <v>0.3208135975485673</v>
       </c>
       <c r="H96">
-        <v>3.982045588328677</v>
+        <v>3.982045498541216</v>
       </c>
       <c r="I96">
-        <v>6.832466998982766E-05</v>
+        <v>6.832469580767216E-05</v>
       </c>
       <c r="J96">
-        <v>0.001039807698286367</v>
+        <v>0.001039808091198524</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5454,6 +5929,11 @@
       <c r="M96" t="inlineStr">
         <is>
           <t>laminin subunit gamma 1 [Source:HGNC Symbol;Acc:HGNC:6492]</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5480,19 +5960,19 @@
         <v>277.1000240253481</v>
       </c>
       <c r="F97">
-        <v>1.597322645611889</v>
+        <v>1.597322645626084</v>
       </c>
       <c r="G97">
-        <v>0.3934615252406367</v>
+        <v>0.3934615302162929</v>
       </c>
       <c r="H97">
-        <v>4.059666684398136</v>
+        <v>4.059666633096271</v>
       </c>
       <c r="I97">
-        <v>4.914281646664987E-05</v>
+        <v>4.914282726339119E-05</v>
       </c>
       <c r="J97">
-        <v>0.0007880619214997996</v>
+        <v>0.0007880620946380388</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5507,6 +5987,11 @@
       <c r="M97" t="inlineStr">
         <is>
           <t>transmembrane protein 170B [Source:HGNC Symbol;Acc:HGNC:34244]</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5533,19 +6018,19 @@
         <v>190.6912490629778</v>
       </c>
       <c r="F98">
-        <v>1.929482320481427</v>
+        <v>1.929482320523841</v>
       </c>
       <c r="G98">
-        <v>0.5136123690415244</v>
+        <v>0.5136123699622628</v>
       </c>
       <c r="H98">
-        <v>3.756689746553656</v>
+        <v>3.756689739901725</v>
       </c>
       <c r="I98">
-        <v>0.0001721757352438475</v>
+        <v>0.0001721757398184155</v>
       </c>
       <c r="J98">
-        <v>0.002266907496344567</v>
+        <v>0.002266907556574439</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5560,6 +6045,11 @@
       <c r="M98" t="inlineStr">
         <is>
           <t>kinesin family member 21B [Source:HGNC Symbol;Acc:HGNC:29442]</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5586,19 +6076,19 @@
         <v>130.1570456550606</v>
       </c>
       <c r="F99">
-        <v>2.269050383628216</v>
+        <v>2.269050383469041</v>
       </c>
       <c r="G99">
-        <v>0.6443074881928204</v>
+        <v>0.6443074858352081</v>
       </c>
       <c r="H99">
-        <v>3.521688673823333</v>
+        <v>3.521688686462641</v>
       </c>
       <c r="I99">
-        <v>0.0004288074056004235</v>
+        <v>0.0004288073851576391</v>
       </c>
       <c r="J99">
-        <v>0.004738695838335498</v>
+        <v>0.004738695206455792</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5613,6 +6103,11 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Rho guanine nucleotide exchange factor 37 [Source:HGNC Symbol;Acc:HGNC:34430]</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5639,19 +6134,19 @@
         <v>292.9193758602179</v>
       </c>
       <c r="F100">
-        <v>1.335488761409969</v>
+        <v>1.335488761321719</v>
       </c>
       <c r="G100">
-        <v>0.3707230637852054</v>
+        <v>0.3707230699329665</v>
       </c>
       <c r="H100">
-        <v>3.602389200645318</v>
+        <v>3.602389140668262</v>
       </c>
       <c r="I100">
-        <v>0.0003153058085987852</v>
+        <v>0.0003153058813701222</v>
       </c>
       <c r="J100">
-        <v>0.00370233893107333</v>
+        <v>0.003702339785558553</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5666,6 +6161,11 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>geminin, DNA replication inhibitor [Source:HGNC Symbol;Acc:HGNC:17493]</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5692,19 +6192,19 @@
         <v>65.12936166818059</v>
       </c>
       <c r="F101">
-        <v>2.383928989747273</v>
+        <v>2.383928990148864</v>
       </c>
       <c r="G101">
-        <v>0.5968062682125956</v>
+        <v>0.5968062716606286</v>
       </c>
       <c r="H101">
-        <v>3.994477130555312</v>
+        <v>3.994477108150222</v>
       </c>
       <c r="I101">
-        <v>6.483717906623786E-05</v>
+        <v>6.483718519705691E-05</v>
       </c>
       <c r="J101">
-        <v>0.0009974901195690885</v>
+        <v>0.0009974902138889141</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5719,6 +6219,11 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>FLVCR1 divergent transcript [Source:HGNC Symbol;Acc:HGNC:39077]</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
         </is>
       </c>
     </row>
@@ -5729,7 +6234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AF29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5830,60 +6335,65 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>comparison_description</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>metabolite_name</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>average_mz</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>average_rt_min</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>bin_base_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ret_index</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>quant_mz</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>bb_id</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mass_spec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>pub_chem</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>kegg</t>
         </is>
@@ -5912,19 +6422,19 @@
         <v>221657.9584088448</v>
       </c>
       <c r="F2">
-        <v>-1.694891439865143</v>
+        <v>-1.694887966351512</v>
       </c>
       <c r="G2">
-        <v>0.4452663986442748</v>
+        <v>0.4452663982878312</v>
       </c>
       <c r="H2">
-        <v>-3.806466072952429</v>
+        <v>-3.806458275021002</v>
       </c>
       <c r="I2">
-        <v>0.0001409666199123287</v>
+        <v>0.0001409710625367258</v>
       </c>
       <c r="J2">
-        <v>0.0002360079788507944</v>
+        <v>0.0002360154167449953</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -5969,6 +6479,11 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -5996,19 +6511,19 @@
         <v>14790.70239307752</v>
       </c>
       <c r="F3">
-        <v>-1.655189108272327</v>
+        <v>-1.655188064249198</v>
       </c>
       <c r="G3">
-        <v>0.2774593005189281</v>
+        <v>0.2774592971030815</v>
       </c>
       <c r="H3">
-        <v>-5.96552036704717</v>
+        <v>-5.965516677692237</v>
       </c>
       <c r="I3">
-        <v>2.438556269132494E-09</v>
+        <v>2.438611373032379E-09</v>
       </c>
       <c r="J3">
-        <v>7.08309962604964E-09</v>
+        <v>7.083259682398396E-09</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6053,6 +6568,11 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6080,19 +6600,19 @@
         <v>18360.65982128734</v>
       </c>
       <c r="F4">
-        <v>-1.134947418350489</v>
+        <v>-1.134943132842278</v>
       </c>
       <c r="G4">
-        <v>0.5184400590731001</v>
+        <v>0.5184400598324599</v>
       </c>
       <c r="H4">
-        <v>-2.189158415689596</v>
+        <v>-2.189150146323663</v>
       </c>
       <c r="I4">
-        <v>0.02858532793429658</v>
+        <v>0.02858592877120384</v>
       </c>
       <c r="J4">
-        <v>0.1301577812971135</v>
+        <v>0.1301556283295327</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -6106,32 +6626,37 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>phenylethylamine</t>
         </is>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>513300</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>174</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>16890</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>86:5896.0 87:600.0 88:548.0 90:188.0 91:2636.0 92:206.0 93:1.0 97:1.0 98:48.0 99:129.0 100:2765.0 101:192.0 102:109.0 103:2633.0 104:279.0 107:378.0 108:74.0 110:55.0 113:65.0 114:106.0 116:481.0 121:196.0 122:31.0 124:2.0 127:165.0 128:135.0 129:158.0 130:745.0 134:29.0 135:9.0 139:10.0 143:120.0 144:297.0 146:47.0 155:163.0 158:53.0 160:164.0 161:9.0 162:213.0 172:80.0 174:6708.0 175:987.0 176:1114.0 177:52.0 179:71.0 184:188.0 185:4.0 186:303.0 188:70.0 189:45.0 204:34.0 205:3.0 215:19.0 216:3.0 219:438.0 220:31.0 243:18.0 250:327.0 251:134.0 271:73.0 272:56.0 288:1.0 289:22.0 299:23.0 300:6.0 404:2.0 467:17.0</t>
         </is>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>1001</v>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>C05332</t>
         </is>
@@ -6160,19 +6685,19 @@
         <v>3336493.36813476</v>
       </c>
       <c r="F5">
-        <v>-1.829341539929361</v>
+        <v>-1.829336385044208</v>
       </c>
       <c r="G5">
-        <v>0.4631009747683288</v>
+        <v>0.4631009742501305</v>
       </c>
       <c r="H5">
-        <v>-3.950200149858265</v>
+        <v>-3.950189023044779</v>
       </c>
       <c r="I5">
-        <v>7.808586752823602E-05</v>
+        <v>7.808949778404184E-05</v>
       </c>
       <c r="J5">
-        <v>0.0001377477271303039</v>
+        <v>0.0001377541310994469</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6217,6 +6742,11 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6244,19 +6774,19 @@
         <v>2614.073358182975</v>
       </c>
       <c r="F6">
-        <v>-2.475094741939752</v>
+        <v>-2.475091033022174</v>
       </c>
       <c r="G6">
-        <v>0.4879436360307566</v>
+        <v>0.4879436416197462</v>
       </c>
       <c r="H6">
-        <v>-5.072501328378302</v>
+        <v>-5.072493669158227</v>
       </c>
       <c r="I6">
-        <v>3.926203940463189E-07</v>
+        <v>3.926362020113446E-07</v>
       </c>
       <c r="J6">
-        <v>9.749602350958351E-07</v>
+        <v>9.749994896468762E-07</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6301,6 +6831,11 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6328,19 +6863,19 @@
         <v>11062.15490718895</v>
       </c>
       <c r="F7">
-        <v>-1.546625868506267</v>
+        <v>-1.546624627739476</v>
       </c>
       <c r="G7">
-        <v>0.2983776335361054</v>
+        <v>0.2983776220172624</v>
       </c>
       <c r="H7">
-        <v>-5.183451085716571</v>
+        <v>-5.183447127445762</v>
       </c>
       <c r="I7">
-        <v>2.178173728571388E-07</v>
+        <v>2.178219977543705E-07</v>
       </c>
       <c r="J7">
-        <v>5.53496661579306E-07</v>
+        <v>5.535084139255231E-07</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6385,6 +6920,11 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6412,19 +6952,19 @@
         <v>13696.33243120745</v>
       </c>
       <c r="F8">
-        <v>-1.403550319798281</v>
+        <v>-1.403549002955882</v>
       </c>
       <c r="G8">
-        <v>0.3025510861094901</v>
+        <v>0.3025510813616631</v>
       </c>
       <c r="H8">
-        <v>-4.639052326159392</v>
+        <v>-4.639048046495359</v>
       </c>
       <c r="I8">
-        <v>3.500104343318905E-06</v>
+        <v>3.50017681532752E-06</v>
       </c>
       <c r="J8">
-        <v>7.727842318777667E-06</v>
+        <v>7.728002328937413E-06</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -6469,6 +7009,11 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6496,19 +7041,19 @@
         <v>611640.8670474482</v>
       </c>
       <c r="F9">
-        <v>-1.643707866928268</v>
+        <v>-1.643702733541014</v>
       </c>
       <c r="G9">
-        <v>0.5110376448293705</v>
+        <v>0.5110376444124153</v>
       </c>
       <c r="H9">
-        <v>-3.216412496337882</v>
+        <v>-3.216402453934529</v>
       </c>
       <c r="I9">
-        <v>0.001298041112415005</v>
+        <v>0.00129808654101519</v>
       </c>
       <c r="J9">
-        <v>0.001837486769522539</v>
+        <v>0.001837551077540983</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -6553,6 +7098,11 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6580,19 +7130,19 @@
         <v>293254.2740349415</v>
       </c>
       <c r="F10">
-        <v>-2.311043865793789</v>
+        <v>-2.311037572803797</v>
       </c>
       <c r="G10">
-        <v>0.5482494668445637</v>
+        <v>0.5482494664809756</v>
       </c>
       <c r="H10">
-        <v>-4.215314387982801</v>
+        <v>-4.215302912445225</v>
       </c>
       <c r="I10">
-        <v>2.494304677074501E-05</v>
+        <v>2.494431518565757E-05</v>
       </c>
       <c r="J10">
-        <v>4.818754651325832E-05</v>
+        <v>4.818999696781419E-05</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -6637,6 +7187,11 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6664,19 +7219,19 @@
         <v>108823.7692776138</v>
       </c>
       <c r="F11">
-        <v>-2.224842136957992</v>
+        <v>-2.224838347152966</v>
       </c>
       <c r="G11">
-        <v>0.4543467994368395</v>
+        <v>0.4543467992987714</v>
       </c>
       <c r="H11">
-        <v>-4.896792801700535</v>
+        <v>-4.896784461972069</v>
       </c>
       <c r="I11">
-        <v>9.741345625266378E-07</v>
+        <v>9.741758880542395E-07</v>
       </c>
       <c r="J11">
-        <v>2.33229211444239E-06</v>
+        <v>2.332391056832752E-06</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -6721,6 +7276,11 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6748,19 +7308,19 @@
         <v>624.9647653734933</v>
       </c>
       <c r="F12">
-        <v>-1.620149805326917</v>
+        <v>-1.620148643823647</v>
       </c>
       <c r="G12">
-        <v>0.3415586911391946</v>
+        <v>0.3415586902830623</v>
       </c>
       <c r="H12">
-        <v>-4.743400906951774</v>
+        <v>-4.743397518244874</v>
       </c>
       <c r="I12">
-        <v>2.101597690503007E-06</v>
+        <v>2.101632862476707E-06</v>
       </c>
       <c r="J12">
-        <v>4.82528693684227E-06</v>
+        <v>4.825367692005832E-06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -6805,6 +7365,11 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6832,19 +7397,19 @@
         <v>166285.5771453603</v>
       </c>
       <c r="F13">
-        <v>-1.958016015982934</v>
+        <v>-1.958010664056297</v>
       </c>
       <c r="G13">
-        <v>0.524204867941221</v>
+        <v>0.5242048676074069</v>
       </c>
       <c r="H13">
-        <v>-3.735211433027909</v>
+        <v>-3.735201225797681</v>
       </c>
       <c r="I13">
-        <v>0.0001875575391844081</v>
+        <v>0.0001875651470075594</v>
       </c>
       <c r="J13">
-        <v>0.0003077905417202133</v>
+        <v>0.0003078030265076509</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6889,6 +7454,11 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -6916,19 +7486,19 @@
         <v>21766.95667850281</v>
       </c>
       <c r="F14">
-        <v>-2.449230998840082</v>
+        <v>-2.449227467677068</v>
       </c>
       <c r="G14">
-        <v>0.4539776102282837</v>
+        <v>0.4539776118130082</v>
       </c>
       <c r="H14">
-        <v>-5.395048001615059</v>
+        <v>-5.395040204506596</v>
       </c>
       <c r="I14">
-        <v>6.850523582829533E-08</v>
+        <v>6.850821076190742E-08</v>
       </c>
       <c r="J14">
-        <v>1.809621727045914E-07</v>
+        <v>1.809700312345794E-07</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6973,6 +7543,11 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7000,19 +7575,19 @@
         <v>281979.7512743868</v>
       </c>
       <c r="F15">
-        <v>-0.5754458096285372</v>
+        <v>-0.5754434415778271</v>
       </c>
       <c r="G15">
-        <v>0.3468957157971801</v>
+        <v>0.3468957158997944</v>
       </c>
       <c r="H15">
-        <v>-1.6588438064337</v>
+        <v>-1.658836979537827</v>
       </c>
       <c r="I15">
-        <v>0.09714727045574303</v>
+        <v>0.09714864648638577</v>
       </c>
       <c r="J15">
-        <v>0.2788486466785217</v>
+        <v>0.2788525963961073</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -7026,32 +7601,37 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>inosine</t>
         </is>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>897434</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>230</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>84524</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>85:1568.0 86:780.0 87:1166.0 88:560.0 89:1904.0 91:15501.0 92:2918.0 93:6326.0 94:1647.0 95:2401.0 97:1081.0 98:220.0 99:1165.0 100:804.0 101:3341.0 102:808.0 103:15276.0 104:2320.0 105:6001.0 106:3197.0 107:1491.0 108:2478.0 109:746.0 110:1136.0 111:1921.0 112:413.0 113:1448.0 114:353.0 115:3043.0 116:2998.0 117:9407.0 118:1635.0 119:4572.0 120:1119.0 121:826.0 122:365.0 123:390.0 124:342.0 125:560.0 126:410.0 127:944.0 128:745.0 129:6916.0 130:1540.0 131:5401.0 132:1978.0 133:6175.0 134:1052.0 135:1120.0 136:222.0 137:272.0 138:1040.0 139:344.0 140:191.0 141:849.0 142:811.0 143:2861.0 144:777.0 145:2410.0 146:921.0 147:12798.0 148:2083.0 149:1405.0 150:419.0 151:246.0 152:120.0 153:663.0 154:185.0 155:440.0 156:241.0 157:1526.0 158:407.0 159:1184.0 160:321.0 161:428.0 162:405.0 163:457.0 164:145.0 165:346.0 166:1117.0 167:411.0 168:208.0 169:2730.0 170:519.0 171:882.0 173:691.0 174:54.0 175:375.0 176:164.0 177:435.0 178:113.0 179:219.0 180:252.0 181:424.0 182:97.0 183:269.0 185:224.0 187:237.0 189:984.0 190:216.0 191:464.0 192:533.0 193:8163.0 194:1429.0 195:390.0 196:128.0 197:189.0 198:108.0 199:326.0 200:119.0 201:222.0 202:120.0 203:192.0 204:365.0 205:434.0 206:405.0 207:1541.0 208:616.0 209:2943.0 210:178.0 211:105.0 212:99.0 213:151.0 215:648.0 216:149.0 217:14712.0 218:2569.0 219:1558.0 220:193.0 221:491.0 222:49.0 223:102.0 224:30.0 225:64.0 226:46.0 227:82.0 229:294.0 230:10605.0 231:2623.0 232:1108.0 233:219.0 234:54.0 235:174.0 236:65.0 237:4677.0 238:892.0 239:211.0 241:29.0 242:28.0 243:3063.0 244:783.0 245:7719.0 246:1654.0 247:734.0 248:192.0 249:188.0 250:21.0 251:82.0 252:42.0 254:26.0 257:230.0 258:750.0 259:3915.0 260:723.0 261:413.0 262:30.0 263:135.0 265:906.0 266:226.0 267:276.0 268:37.0 276:34.0 278:44.0 279:101.0 280:1223.0 281:4422.0 282:1184.0 283:433.0 284:94.0 291:143.0 292:91.0 293:26.0 294:88.0 295:35.0 296:32.0 299:31.0 305:29.0 306:92.0 307:1260.0 308:271.0 309:291.0 310:14.0 311:66.0 312:10.0 317:31.0 318:22.0 319:64.0 320:133.0 321:116.0 322:119.0 323:779.0 324:199.0 326:11.0 327:15.0 331:13.0 333:103.0 335:325.0 336:60.0 337:52.0 338:133.0 339:61.0 347:48.0 348:564.0 349:219.0 350:68.0 351:53.0 361:52.0 362:25.0 363:184.0 364:62.0 366:9.0 377:55.0 379:48.0 394:15.0 395:329.0 396:139.0 397:11.0 424:12.0 437:5.0 452:49.0 453:187.0 454:90.0 465:36.0 466:74.0 467:21.0 468:21.0 469:23.0</t>
         </is>
       </c>
-      <c r="AD15">
+      <c r="AE15">
         <v>6021</v>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>C00294</t>
         </is>
@@ -7080,19 +7660,19 @@
         <v>523.0774307646341</v>
       </c>
       <c r="F16">
-        <v>-1.785831779102629</v>
+        <v>-1.785830687732123</v>
       </c>
       <c r="G16">
-        <v>0.3401603943246572</v>
+        <v>0.3401603919314415</v>
       </c>
       <c r="H16">
-        <v>-5.249969746325578</v>
+        <v>-5.249966574862286</v>
       </c>
       <c r="I16">
-        <v>1.52124192597137E-07</v>
+        <v>1.521268116937376E-07</v>
       </c>
       <c r="J16">
-        <v>3.918522423739685E-07</v>
+        <v>3.91858988828023E-07</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -7137,6 +7717,11 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7164,19 +7749,19 @@
         <v>786127.385482633</v>
       </c>
       <c r="F17">
-        <v>-0.0770725111705836</v>
+        <v>-0.07707072711002308</v>
       </c>
       <c r="G17">
-        <v>0.2907177297111358</v>
+        <v>0.2907177296052843</v>
       </c>
       <c r="H17">
-        <v>-0.2651111483539883</v>
+        <v>-0.2651050117055612</v>
       </c>
       <c r="I17">
-        <v>0.7909238393876301</v>
+        <v>0.7909285666499049</v>
       </c>
       <c r="J17">
-        <v>0.9055629861647948</v>
+        <v>0.9055658333000849</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -7190,32 +7775,37 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>glycine</t>
         </is>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>368707</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>248</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>6</v>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>85:2882.0 86:87494.0 87:10917.0 88:4018.0 89:822.0 92:65.0 93:42.0 94:27.0 95:426.0 96:50.0 97:67.0 99:1489.0 100:53029.0 101:10140.0 102:5892.0 103:928.0 105:1276.0 110:146.0 113:1787.0 114:44.0 115:2820.0 116:1864.0 117:12472.0 118:47.0 119:3422.0 122:40.0 123:85.0 125:63.0 129:156.0 130:9640.0 131:7466.0 132:862.0 133:31722.0 134:5661.0 135:2633.0 144:2949.0 145:349.0 146:1208.0 147:26782.0 148:8179.0 149:5445.0 158:2433.0 159:1298.0 160:2359.0 161:551.0 162:205.0 163:69.0 171:65.0 172:1683.0 174:152336.0 175:28023.0 176:12302.0 177:361.0 178:255.0 187:150.0 188:2043.0 190:449.0 191:115.0 200:60.0 202:783.0 203:236.0 204:837.0 205:85.0 218:58.0 246:286.0 248:21677.0 249:5746.0 250:2638.0 251:499.0 253:40.0 254:32.0 258:17.0 263:51.0 267:29.0 268:34.0 276:4493.0 277:408.0 278:257.0 288:36.0 292:28.0 299:12.0 304:15.0 305:20.0 318:38.0 322:24.0 326:35.0 334:37.0 341:26.0 344:23.0 345:20.0 346:12.0 356:14.0 381:30.0 417:22.0 433:16.0 440:27.0 454:22.0 458:43.0 459:16.0 461:27.0</t>
         </is>
       </c>
-      <c r="AD17">
+      <c r="AE17">
         <v>750</v>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>C00037</t>
         </is>
@@ -7244,19 +7834,19 @@
         <v>33221.00365071683</v>
       </c>
       <c r="F18">
-        <v>-0.7823654775777187</v>
+        <v>-0.782363524320956</v>
       </c>
       <c r="G18">
-        <v>0.3538903759937287</v>
+        <v>0.3538903758628231</v>
       </c>
       <c r="H18">
-        <v>-2.210756580709002</v>
+        <v>-2.210751062143097</v>
       </c>
       <c r="I18">
-        <v>0.02705269804932188</v>
+        <v>0.02705308041052645</v>
       </c>
       <c r="J18">
-        <v>0.1263002469170148</v>
+        <v>0.1263020320370964</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -7270,32 +7860,37 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>nicotinamide</t>
         </is>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>471602</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>179</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>84542</v>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>86:209.0 89:162.0 90:198.0 92:127.0 93:263.0 94:195.0 100:836.0 102:136.0 103:220.0 104:2595.0 105:4174.0 106:810.0 108:61.0 119:174.0 120:170.0 122:157.0 123:39.0 135:126.0 136:6136.0 137:808.0 138:240.0 139:45.0 148:164.0 150:54.0 151:55.0 161:87.0 163:218.0 164:32.0 165:80.0 166:33.0 175:86.0 178:33.0 179:15388.0 180:2109.0 181:675.0 182:48.0 193:1190.0 194:529.0 195:117.0</t>
         </is>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>936</v>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>C00153</t>
         </is>
@@ -7324,19 +7919,19 @@
         <v>196887.1816547048</v>
       </c>
       <c r="F19">
-        <v>-2.362662230582311</v>
+        <v>-2.362655128764501</v>
       </c>
       <c r="G19">
-        <v>0.5717156851239392</v>
+        <v>0.5717156853405357</v>
       </c>
       <c r="H19">
-        <v>-4.132582491715479</v>
+        <v>-4.132570068210065</v>
       </c>
       <c r="I19">
-        <v>3.587099621068113E-05</v>
+        <v>3.587293577010809E-05</v>
       </c>
       <c r="J19">
-        <v>6.741273425800421E-05</v>
+        <v>6.74163792920997E-05</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -7381,6 +7976,11 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7408,19 +8008,19 @@
         <v>23252.54899381875</v>
       </c>
       <c r="F20">
-        <v>-1.295114280507605</v>
+        <v>-1.295112163242666</v>
       </c>
       <c r="G20">
-        <v>0.376188915593763</v>
+        <v>0.3761889156651158</v>
       </c>
       <c r="H20">
-        <v>-3.442723128786088</v>
+        <v>-3.442717499937126</v>
       </c>
       <c r="I20">
-        <v>0.000575888574476404</v>
+        <v>0.0005759005600930604</v>
       </c>
       <c r="J20">
-        <v>0.009806256096240034</v>
+        <v>0.009806408643211939</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -7434,32 +8034,37 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>uridine</t>
         </is>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>861508</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>217</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>14815</v>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>85:38.0 86:16.0 87:11.0 88:11.0 89:85.0 91:9.0 92:3.0 93:5.0 94:11.0 95:26.0 97:5.0 99:146.0 100:46.0 101:72.0 103:551.0 104:39.0 105:323.0 107:5.0 109:17.0 110:8.0 111:3.0 112:3.0 113:55.0 114:1.0 115:80.0 116:27.0 117:70.0 118:2.0 119:12.0 121:6.0 122:6.0 125:1.0 127:42.0 129:189.0 130:39.0 131:87.0 132:7.0 133:129.0 134:30.0 135:16.0 136:2.0 137:1.0 138:2.0 140:13.0 141:13.0 142:8.0 143:122.0 145:4.0 146:6.0 147:292.0 148:117.0 149:29.0 152:2.0 153:23.0 154:15.0 155:18.0 157:13.0 161:6.0 163:8.0 165:2.0 167:8.0 168:9.0 169:326.0 170:33.0 171:29.0 172:5.0 173:5.0 174:28.0 175:8.0 179:4.0 180:4.0 183:11.0 184:14.0 185:50.0 186:5.0 187:4.0 188:9.0 189:36.0 191:111.0 192:7.0 193:22.0 197:2.0 200:3.0 202:40.0 203:16.0 204:88.0 205:2.0 206:6.0 207:29.0 208:6.0 211:23.0 213:41.0 215:17.0 216:17.0 217:933.0 218:189.0 219:95.0 222:8.0 223:24.0 224:7.0 225:2.0 226:9.0 227:3.0 228:3.0 229:6.0 230:28.0 231:18.0 232:3.0 233:1.0 235:1.0 237:2.0 239:2.0 240:4.0 242:1.0 243:83.0 244:16.0 245:53.0 247:1.0 249:1.0 250:3.0 253:1.0 257:17.0 258:25.0 259:171.0 260:27.0 261:13.0 262:6.0 263:9.0 265:14.0 267:9.0 269:2.0 271:6.0 276:6.0 278:5.0 279:1.0 280:9.0 281:4.0 282:10.0 283:4.0 284:4.0 289:2.0 294:3.0 299:25.0 301:2.0 302:3.0 304:8.0 310:10.0 311:1.0 312:1.0 314:5.0 315:15.0 316:2.0 317:3.0 322:4.0 324:4.0 325:2.0 326:5.0 329:2.0 330:1.0 331:2.0 333:39.0 334:6.0 335:4.0 336:2.0 337:2.0 338:3.0 339:2.0 341:4.0 343:2.0 346:4.0 348:6.0 351:5.0 357:6.0 363:3.0 364:5.0 367:1.0 368:2.0 369:1.0 370:7.0 372:9.0 374:5.0 375:5.0 377:2.0 378:7.0 379:1.0 381:2.0 385:1.0 386:2.0 387:2.0 392:1.0 393:2.0 394:5.0 396:7.0 397:7.0 403:5.0 406:6.0 408:7.0 410:6.0 412:4.0 413:1.0 415:1.0 417:2.0 418:2.0 419:3.0 422:1.0 425:4.0 429:5.0 431:1.0 433:4.0 435:2.0 436:5.0 437:7.0 438:1.0 442:6.0 443:2.0 446:7.0 448:1.0 450:6.0 451:5.0 454:2.0 457:5.0 460:2.0 461:5.0 463:7.0 464:2.0 465:4.0 467:3.0 474:2.0 478:9.0 481:4.0 489:3.0 491:2.0 492:1.0 493:3.0 494:2.0 499:14.0 500:3.0</t>
         </is>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>6029</v>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>C00299</t>
         </is>
@@ -7488,19 +8093,19 @@
         <v>29923.74764064854</v>
       </c>
       <c r="F21">
-        <v>-1.456990485272161</v>
+        <v>-1.45698849801887</v>
       </c>
       <c r="G21">
-        <v>0.3499426303699391</v>
+        <v>0.3499426330657146</v>
       </c>
       <c r="H21">
-        <v>-4.163512412682945</v>
+        <v>-4.163506701812086</v>
       </c>
       <c r="I21">
-        <v>3.133889803260162E-05</v>
+        <v>3.133968224885479E-05</v>
       </c>
       <c r="J21">
-        <v>5.970824086984173E-05</v>
+        <v>5.970973499298829E-05</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -7545,6 +8150,11 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7572,19 +8182,19 @@
         <v>15372.27753750906</v>
       </c>
       <c r="F22">
-        <v>-0.5504820846729976</v>
+        <v>-0.5504805526747808</v>
       </c>
       <c r="G22">
-        <v>0.3183176182029586</v>
+        <v>0.3183176178260516</v>
       </c>
       <c r="H22">
-        <v>-1.729348465789322</v>
+        <v>-1.729343655039532</v>
       </c>
       <c r="I22">
-        <v>0.08374674736831493</v>
+        <v>0.08374760785486182</v>
       </c>
       <c r="J22">
-        <v>0.2575544809938257</v>
+        <v>0.2575571273314203</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -7598,32 +8208,37 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>asparagine</t>
         </is>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>553743</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>231</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>369588</v>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>85:5318.0 86:8685.0 87:4286.0 88:2645.0 89:20925.0 90:4572.0 91:1167.0 97:786.0 98:10621.0 99:4490.0 100:67427.0 101:13050.0 102:12363.0 103:140095.0 104:14184.0 105:14434.0 106:985.0 109:425.0 111:1873.0 112:1768.0 113:2060.0 114:17369.0 115:21135.0 116:183956.0 117:33418.0 118:14247.0 119:6078.0 120:784.0 125:6198.0 126:2492.0 127:2444.0 128:10059.0 129:22124.0 130:19769.0 131:39679.0 132:82439.0 133:51710.0 134:9431.0 135:2633.0 136:486.0 140:1742.0 141:59818.0 142:13008.0 143:11485.0 144:7122.0 145:4238.0 146:3169.0 147:108415.0 148:19458.0 149:19445.0 150:1971.0 152:558.0 153:1115.0 154:1789.0 155:1181.0 158:3297.0 159:20666.0 160:18954.0 161:3495.0 162:835.0 163:2768.0 164:334.0 168:1258.0 169:3984.0 170:1987.0 171:2096.0 172:7138.0 174:7458.0 175:1604.0 176:1498.0 177:1407.0 186:1742.0 188:47064.0 189:26187.0 190:12304.0 191:6996.0 192:1101.0 193:958.0 196:190.0 198:1097.0 199:2517.0 200:2361.0 201:1340.0 202:15559.0 203:3319.0 204:12201.0 205:7494.0 206:3602.0 207:2564.0 213:2982.0 214:1643.0 215:8286.0 216:7547.0 217:57521.0 218:24147.0 219:8906.0 220:1814.0 221:2097.0 222:733.0 223:361.0 227:290.0 228:862.0 229:1158.0 230:1386.0 231:49175.0 232:11970.0 233:7223.0 234:1691.0 235:379.0 236:86.0 242:1475.0 243:2896.0 244:1899.0 245:1795.0 246:203.0 249:260.0 251:180.0 256:414.0 257:713.0 258:8958.0 259:3135.0 260:1043.0 261:517.0 262:1676.0 263:340.0 264:505.0 272:587.0 274:509.0 275:353.0 277:3651.0 278:1536.0 279:798.0 280:168.0 286:89.0 288:809.0 302:167.0 304:168.0 305:521.0 306:550.0 307:15673.0 308:4903.0 309:2260.0 310:606.0 311:344.0 316:1485.0 317:739.0 318:414.0 331:319.0 332:323.0 333:2771.0 334:579.0 335:535.0 337:90.0 338:92.0 339:69.0 348:1645.0 350:249.0 351:196.0 362:276.0 364:346.0 371:95.0 387:75.0 404:73.0 409:71.0 416:92.0 419:68.0 421:86.0 440:62.0 444:36.0 458:48.0 461:95.0 467:149.0 469:76.0 471:39.0 482:67.0 489:55.0 497:59.0</t>
         </is>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>6267</v>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>C00152</t>
         </is>
@@ -7652,19 +8267,19 @@
         <v>1252.140804014892</v>
       </c>
       <c r="F23">
-        <v>-1.417573923717935</v>
+        <v>-1.417573101965984</v>
       </c>
       <c r="G23">
-        <v>0.2856368540956704</v>
+        <v>0.2856368556362865</v>
       </c>
       <c r="H23">
-        <v>-4.962853719300299</v>
+        <v>-4.962850815621075</v>
       </c>
       <c r="I23">
-        <v>6.946490010679295E-07</v>
+        <v>6.946593900572058E-07</v>
       </c>
       <c r="J23">
-        <v>1.696483586334531E-06</v>
+        <v>1.696508958500558E-06</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -7709,6 +8324,11 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7736,19 +8356,19 @@
         <v>6688.992957690956</v>
       </c>
       <c r="F24">
-        <v>-2.205207485860196</v>
+        <v>-2.205205792267142</v>
       </c>
       <c r="G24">
-        <v>0.3577251594760102</v>
+        <v>0.3577251465697849</v>
       </c>
       <c r="H24">
-        <v>-6.164530023804717</v>
+        <v>-6.16452551187075</v>
       </c>
       <c r="I24">
-        <v>7.069278375485064E-10</v>
+        <v>7.069479934890944E-10</v>
       </c>
       <c r="J24">
-        <v>2.109578604557575E-09</v>
+        <v>2.109638752904776E-09</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -7793,6 +8413,11 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7820,19 +8445,19 @@
         <v>486.8595160177968</v>
       </c>
       <c r="F25">
-        <v>-1.56173476421557</v>
+        <v>-1.561732795777398</v>
       </c>
       <c r="G25">
-        <v>0.4374138766578578</v>
+        <v>0.4374138752393374</v>
       </c>
       <c r="H25">
-        <v>-3.570382302793628</v>
+        <v>-3.570377814199134</v>
       </c>
       <c r="I25">
-        <v>0.0003564605952583431</v>
+        <v>0.0003564667038525604</v>
       </c>
       <c r="J25">
-        <v>0.0005575754477190548</v>
+        <v>0.0005575850027784386</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -7877,6 +8502,11 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -7904,19 +8534,19 @@
         <v>55262.5471321705</v>
       </c>
       <c r="F26">
-        <v>-0.6885752987010932</v>
+        <v>-0.688572860618764</v>
       </c>
       <c r="G26">
-        <v>0.3783044589627757</v>
+        <v>0.3783044590280956</v>
       </c>
       <c r="H26">
-        <v>-1.820161730551655</v>
+        <v>-1.82015528547504</v>
       </c>
       <c r="I26">
-        <v>0.06873437912903756</v>
+        <v>0.06873536034438416</v>
       </c>
       <c r="J26">
-        <v>0.2265729266039447</v>
+        <v>0.2265694445240184</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -7930,32 +8560,37 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>xanthine</t>
         </is>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>701688</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>353</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>1669</v>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>85:2517.0 86:3710.0 87:2079.0 88:382.0 89:398.0 90:80.0 91:121.0 92:294.0 93:389.0 94:217.0 95:887.0 96:502.0 97:447.0 98:2556.0 99:3280.0 100:20394.0 101:2912.0 102:1806.0 103:2337.0 104:350.0 105:1446.0 106:113.0 107:15.0 108:151.0 109:225.0 110:796.0 111:2460.0 112:928.0 113:1375.0 114:1007.0 115:2460.0 116:1524.0 117:4430.0 118:716.0 119:955.0 120:203.0 121:149.0 122:214.0 123:385.0 124:753.0 125:1299.0 126:927.0 127:713.0 128:2133.0 129:570.0 130:2669.0 131:17683.0 132:4507.0 133:9141.0 134:902.0 135:654.0 136:317.0 137:441.0 138:525.0 139:911.0 140:685.0 141:1032.0 142:1839.0 143:1189.0 144:1769.0 145:616.0 146:309.0 147:84747.0 148:13824.0 149:7320.0 150:878.0 151:744.0 152:820.0 153:846.0 154:569.0 155:716.0 156:1197.0 157:2430.0 158:11345.0 159:2439.0 160:1405.0 161:291.0 162:120.0 163:70.0 164:555.0 165:318.0 166:708.0 167:738.0 168:653.0 169:1526.0 170:892.0 171:1982.0 172:2044.0 173:1365.0 174:2816.0 175:583.0 176:255.0 177:155.0 178:451.0 179:306.0 180:690.0 181:1323.0 182:625.0 183:1021.0 184:830.0 185:665.0 186:246.0 187:124.0 188:314.0 189:201.0 190:113.0 191:118.0 192:172.0 193:266.0 194:461.0 195:394.0 196:455.0 197:832.0 198:817.0 199:334.0 200:215.0 201:63.0 202:47.0 203:31.0 204:167.0 205:787.0 206:1099.0 207:789.0 208:613.0 209:498.0 210:743.0 211:589.0 212:251.0 213:64.0 214:219.0 215:112.0 216:56.0 217:96.0 218:145.0 219:194.0 220:462.0 221:1323.0 222:1301.0 223:1229.0 224:983.0 225:547.0 226:281.0 227:208.0 228:106.0 229:77.0 230:44.0 231:56.0 232:97.0 233:15.0 234:67.0 235:410.0 236:1550.0 237:1053.0 238:5251.0 239:1475.0 240:674.0 241:319.0 242:103.0 244:3.0 245:53.0 246:38.0 247:136.0 248:12.0 249:383.0 250:326.0 251:653.0 252:1364.0 253:811.0 254:591.0 255:251.0 256:306.0 257:108.0 259:8.0 260:48.0 261:54.0 262:56.0 263:1232.0 264:341.0 265:5889.0 266:1421.0 267:607.0 268:486.0 269:755.0 270:251.0 271:181.0 272:93.0 273:51.0 274:67.0 275:14.0 276:24.0 277:437.0 278:4264.0 279:13335.0 280:4864.0 281:3735.0 282:997.0 283:538.0 284:211.0 285:94.0 286:59.0 287:83.0 288:27.0 289:9.0 290:7.0 291:44.0 292:36.0 293:652.0 294:16947.0 295:7531.0 296:3125.0 297:797.0 298:263.0 299:77.0 300:79.0 302:54.0 304:6.0 308:30.0 309:152.0 310:369.0 311:818.0 312:371.0 313:142.0 314:55.0 316:18.0 317:35.0 319:21.0 320:37.0 321:12.0 322:49.0 323:114.0 324:148.0 325:192.0 326:1336.0 327:810.0 328:304.0 329:95.0 330:58.0 332:23.0 334:35.0 335:26.0 336:37.0 337:1290.0 338:593.0 339:377.0 340:221.0 341:145.0 342:29.0 343:35.0 347:26.0 348:24.0 349:19.0 350:13.0 351:242.0 352:1176.0 353:49940.0 354:17591.0 355:8417.0 356:1768.0 357:564.0 358:92.0 359:65.0 360:46.0 361:93.0 362:121.0 363:132.0 364:132.0 366:36.0 367:1739.0 368:18993.0 369:6547.0 370:3076.0 371:677.0 372:202.0 373:42.0 374:31.0 377:12.0 378:2.0 385:7.0 388:43.0 390:48.0 391:36.0 393:14.0 398:1.0 403:4.0 404:9.0 406:32.0 409:21.0 422:6.0 424:5.0 425:35.0 437:29.0 438:5.0 439:16.0 455:12.0 457:3.0 459:12.0 471:6.0 476:11.0 487:21.0 493:16.0 496:21.0 500:29.0</t>
         </is>
       </c>
-      <c r="AD26">
+      <c r="AE26">
         <v>1188</v>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>C00385</t>
         </is>
@@ -7984,19 +8619,19 @@
         <v>634704.1804760132</v>
       </c>
       <c r="F27">
-        <v>-2.59803377627575</v>
+        <v>-2.598025591488951</v>
       </c>
       <c r="G27">
-        <v>0.6284941962668987</v>
+        <v>0.6284941959255443</v>
       </c>
       <c r="H27">
-        <v>-4.133743464470211</v>
+        <v>-4.133730443863528</v>
       </c>
       <c r="I27">
-        <v>3.569018377225689E-05</v>
+        <v>3.569220682282655E-05</v>
       </c>
       <c r="J27">
-        <v>6.713385158251046E-05</v>
+        <v>6.713765697554385E-05</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -8041,6 +8676,11 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -8068,19 +8708,19 @@
         <v>5460572.735289546</v>
       </c>
       <c r="F28">
-        <v>-1.089624122436002</v>
+        <v>-1.089622063588068</v>
       </c>
       <c r="G28">
-        <v>0.3090412618830461</v>
+        <v>0.3090458699631412</v>
       </c>
       <c r="H28">
-        <v>-3.52582084281147</v>
+        <v>-3.525761608521166</v>
       </c>
       <c r="I28">
-        <v>0.000422172458477732</v>
+        <v>0.0004222668888391674</v>
       </c>
       <c r="J28">
-        <v>0.0006486047192191267</v>
+        <v>0.0006487497973189286</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -8125,6 +8765,11 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>bioamines</t>
         </is>
       </c>
@@ -8152,19 +8797,19 @@
         <v>7360.015546120624</v>
       </c>
       <c r="F29">
-        <v>-0.1112874528407569</v>
+        <v>-0.111285083796445</v>
       </c>
       <c r="G29">
-        <v>0.3883974734267192</v>
+        <v>0.3883974733565205</v>
       </c>
       <c r="H29">
-        <v>-0.2865298063318994</v>
+        <v>-0.286523706847839</v>
       </c>
       <c r="I29">
-        <v>0.7744723678371155</v>
+        <v>0.7744770387944324</v>
       </c>
       <c r="J29">
-        <v>0.9017819268007354</v>
+        <v>0.9017784247121901</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -8178,32 +8823,37 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>log2 fold change (MLE): treatment cancerous vs normal_adjacent</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>pm</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>hypotaurine</t>
         </is>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>525092</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>188</v>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <v>31223</v>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>86:1014.0 87:116.0 88:90.0 89:68.0 90:17.0 91:63.0 92:40.0 94:26.0 98:37.0 99:240.0 100:6173.0 101:708.0 102:301.0 103:213.0 104:146.0 105:183.0 106:48.0 110:49.0 113:142.0 114:1274.0 117:377.0 118:68.0 119:29.0 120:26.0 121:58.0 122:28.0 123:14.0 126:44.0 127:49.0 128:31.0 129:49.0 130:843.0 131:338.0 133:665.0 134:59.0 135:121.0 136:23.0 137:78.0 140:230.0 141:34.0 142:206.0 144:249.0 145:134.0 146:62.0 147:1218.0 148:590.0 151:21.0 156:135.0 157:203.0 158:127.0 159:91.0 160:61.0 162:21.0 163:18.0 164:6.0 166:27.0 172:656.0 173:198.0 174:1048.0 175:181.0 176:426.0 177:41.0 178:56.0 183:41.0 186:161.0 188:4497.0 189:697.0 190:288.0 191:53.0 194:45.0 195:20.0 202:15.0 210:20.0 212:21.0 215:25.0 216:24.0 222:44.0 223:13.0 226:21.0 231:14.0 240:24.0 241:19.0 247:15.0 248:54.0 250:16.0 251:14.0 253:27.0 254:14.0 255:29.0 266:17.0 267:28.0 268:26.0 269:20.0 274:16.0 275:28.0 276:15.0 279:19.0 283:30.0 284:25.0 285:12.0 287:26.0 288:33.0 293:14.0 294:17.0 295:20.0 298:16.0 302:21.0 303:22.0 307:25.0 309:15.0 310:120.0 311:47.0 312:18.0 314:146.0 317:12.0 319:31.0 322:26.0 325:17.0 327:21.0 332:20.0 334:16.0 336:26.0 337:13.0 338:13.0 339:7.0 341:27.0 343:20.0 345:19.0 346:24.0 347:25.0 348:20.0 350:14.0 351:18.0 361:16.0 362:13.0 365:14.0 381:17.0 388:22.0 390:11.0 394:13.0 399:13.0 402:25.0 403:29.0 407:15.0 410:26.0 417:20.0 421:14.0 426:12.0 432:17.0 445:20.0 447:7.0 457:8.0 462:11.0 464:27.0 469:12.0 475:20.0 488:11.0</t>
         </is>
       </c>
-      <c r="AD29">
+      <c r="AE29">
         <v>107812</v>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>C00519</t>
         </is>
